--- a/v4/물품계획서_근거.xlsx
+++ b/v4/물품계획서_근거.xlsx
@@ -2345,11 +2345,11 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>출력 전체 4.05kg + 실패 여유 15% + 핸들 받침 → 약 5kg</t>
+          <t>출력 전체 4.66kg (핸들 받침 포함) + 실패 여유 15% = 5.36kg → 750g 8롤 (6kg)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">

--- a/v4/물품계획서_근거.xlsx
+++ b/v4/물품계획서_근거.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
+    <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -529,32 +529,32 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>변속기 19 (끝판 4 · 출력 기어 12 · 아이들러 2 · 클러치 파일럿 1) + 핸들 4 (축 2 · 롤러 2) + 여분 2</t>
+          <t>변속기 19 (끝판 4 · 출력 기어 12 · 아이들러 2 · 클러치 파일럿 1) + 핸들 3 (축 2 · 롤러 1) + 여분 3</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 무명 10개 묶음 → NSK: 바깥지름 공차가 고르게 작아 쿠폰으로 정한 압입 구멍이 모두 맞고 소리가 작음</t>
+          <t>NSK: 바깥지름 공차가 고르게 작아 쿠폰으로 정한 압입 구멍이 모두 맞고 소리가 작음. 11번가 2569692102 에는 6001 옵션이 없어 같은 판매자(소망트레이딩) 상품으로</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>NSK 6001ZZ, 12×28×8, 철판 실드(ZZ)</t>
+          <t>NSK 6001ZZ, 12×28×8, 철판 실드(ZZ). 옵션 "NSK 6001 ZZ"</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2569692102</t>
+          <t>https://www.11st.co.kr/products/1432577678</t>
         </is>
       </c>
     </row>
@@ -582,22 +582,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>같은 이유로 NSK</t>
+          <t>같은 이유로 NSK (1번과 같은 상품)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>NSK 6003ZZ, 17×35×10</t>
+          <t>NSK 6003ZZ, 17×35×10. 옵션 "NSK 6003 ZZ"</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -606,18 +606,18 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="35" customHeight="1">
+    <row r="4" ht="95" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>연마봉 Ø12 S45C 1m (열처리 안 된 것)</t>
+          <t>SM45C 마봉 Ø12 1m 6개 (열처리 안 된 것)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>435·358·160 으로 절단</t>
+          <t>Ø12 × 1000, 6개 세트</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>입력축 435 · 출력축 358 (D컷은 직접: 그라인더 + 줄) · 레버봉 160</t>
+          <t>봉 1: 입력축 435 · 출력축 358 · 레버봉 160 / 봉 2: 핸들 축 106 · 롤러 핀 22 · 아이들러 축 55 / 봉 3~6: D컷 실수 대비 (모두 절단석으로 직접 자름)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>소망트레이딩의 G마켓 상품. 줄로 다듬어야 하므로 열처리 안 된 S45C</t>
+          <t>G마켓 소망트레이딩 연마봉이 지워졌고, 쿠팡·11번가의 Ø12 연마봉은 모두 열처리품이라 줄로 D컷을 못 함 → 열처리 안 된 SM45C 마봉. 연마(h7)가 아니므로 받으면 지름을 잼 (11.95 보다 가늘면 끝판 베어링 자리에 록타이트 243)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>지름 12 연마(h7), 열처리 안 됨, 절단 435·358·160 (주문 메모)</t>
+          <t>SM45C, Ø12, 1m × 6, 열처리 안 됨. 옵션 "SM45C /직경12mm/1m6개 × 1세트"</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>smball 1m 16,000 기준</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=2295287294</t>
+          <t>https://www.coupang.com/vp/products/9472297916</t>
         </is>
       </c>
     </row>
@@ -660,45 +660,45 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>연마봉 Ø12 S45C 1m (여분, 열처리 안 된 것)</t>
+          <t>스텐 환봉 Ø6 1m</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>자르지 않음</t>
+          <t>자르지 않은 1m (371mm 2개씩 직접 자름)</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>D컷 실수 대비 (입력·출력축 다시 자를 길이) + 핸들 축 140 · 롤러 핀 22 (앵글 그라인더로 자름)</t>
+          <t>변속 레일 3 + 여분 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
+          <t>G마켓 상품을 열 수 없어 쿠팡 국내 상품으로. 절단 옵션이 없어 절단석으로 자르고 끝을 줄로 모따기</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>위와 같은 봉</t>
+          <t>스텐, 지름 6, 1m. 옵션 "국내최초 스텐환봉 절단판매 1M (6파이)"</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>smball 1m 16,000 기준</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=2295287294</t>
+          <t>https://www.coupang.com/vp/products/7575963441</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>연마봉 Ø12 S45C 10cm</t>
+          <t>강철 평행핀 Ø5×25</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55 로 절단</t>
+          <t>100개, 공차 0~+0.01</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -721,80 +721,80 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>후진 아이들러 축</t>
+          <t>도그 24 + 여분</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>같은 판매자</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>옵션 "12파이-10cm", 메모에 55mm</t>
+          <t>옵션 "M5 (+)공차 / 25mm × 100개"</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=2295287294</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9743421687</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>스텐 환봉 Ø6 1m</t>
+          <t>강철 평행핀 Ø5×40</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>371mm 2개로 절단</t>
+          <t>공차 0~+0.01</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>변속 레일 3 + 여분 1</t>
+          <t>스프로킷 커플링 6 + 여분 2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>소망 6파이는 G마켓에 없음 → 스텐 환봉 절단판매 (무른 재질이라 러그·칼라 나사 끝이 잘 물림)</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>지름 6, 1m 3,000 + 절단 2번 500×2 → 371mm 2개씩</t>
+          <t>옵션 "(+) 0~+0.01 × 5x40"</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=692264521</t>
+          <t>https://www.coupang.com/vp/products/8532354386</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>강철 평행핀 Ø5×25</t>
+          <t>고무 호스</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>100개, 공차 0~+0.01</t>
+          <t>안지름 5 × 바깥지름 10, 약 2m</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -817,22 +817,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>도그 24 + 여분</t>
+          <t>핀 쿠션 6mm × 24 (144mm)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>그대로. 재질 표기 없음(진공호스) → 받으면 바깥지름을 재서 CUSH_OD</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M5 (+)공차 / 25mm × 100개"</t>
+          <t>안 5 × 바깥 10</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9743421687</t>
+          <t>https://www.coupang.com/vp/products/8558801755</t>
         </is>
       </c>
     </row>
@@ -852,35 +852,35 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>강철 평행핀 Ø5×40</t>
+          <t>큰 와셔 DIN9021 M16 스텐</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>공차 0~+0.01</t>
+          <t>17×50×3</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>스프로킷 커플링 6 + 여분 2</t>
+          <t>클러치 원판 1 + 여분 1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>여분 2 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5x40 낱개</t>
+          <t>옵션 "M16 × 50mm"</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8532354386</t>
+          <t>https://www.coupang.com/vp/products/6305734042</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NBR 고무 호스</t>
+          <t>코르크 시트</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>안지름 5 × 바깥지름 10, 약 2m</t>
+          <t>2mm, A4 2매</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>핀 쿠션 6mm × 24 (144mm)</t>
+          <t>클러치 마찰 링 2 (바깥 Ø50, 안 Ø26)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>안 5 × 바깥 10</t>
+          <t>옵션 "콜크쉬트:연갈색 2mm×A4×2매"</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8558801755</t>
+          <t>https://www.coupang.com/vp/products/4845669553</t>
         </is>
       </c>
     </row>
@@ -948,20 +948,20 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>큰 와셔 DIN9021 M16 스텐</t>
+          <t>강구</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17×50×3</t>
+          <t>Ø6, 50개</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>클러치 원판 1 + 여분 1</t>
+          <t>러그 디텐트 3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M16 × 50mm"</t>
+          <t>지름 6, 옵션 "50개"</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -986,93 +986,93 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6305734042</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9638493021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>코르크 시트</t>
+          <t>샤프트 칼라 Ø6 (무두볼트 고정)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2mm, A4 2매</t>
+          <t>안 6 · 바깥 12 · 폭 6</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>클러치 마찰 링 2 (바깥 Ø50, 안 Ø26)</t>
+          <t>레일 카트리지 6 + 여분 4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>쿠팡 SCC6 은 모두 해외배송, 11번가는 국내 상품 없음 → G마켓 국내 상품 (검색 결과에 "국내배송만 가능"). G마켓 화면은 이 환경·다른 세션 모두 못 열어 사용자가 확인</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>두께 2</t>
+          <t>안지름 6, 바깥지름 12.5 이하 (카트리지 구멍 13), 폭 8 이하, 강철, 국내배송. 옵션 "SCC6 6-12-6"</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>추정 (G마켓 화면 미확인)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/4845669553</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
+          <t>https://item.gmarket.co.kr/Item?goodscode=4101441390</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="95" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>강구</t>
+          <t>압축 스프링 SUS304 (C252 대신)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ø6, 50개</t>
+          <t>선경 1.5 · 외경 18 · 자유장 25</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>러그 디텐트 3</t>
+          <t>변속기 9 (포크 카트리지 3 · 클러치 3 · 레버 후진 잠금 1 · 페달 복귀 2) + 핸들 복귀 2 + 여분 4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>판매 중인 기성품 (사용자 결정). 사진으로 센 권수 5.5 → k ≈ 2.8 N/mm, 밀착 8.3. 자유장이 C252(32)보다 짧아 카트리지·클러치 컵·레버 스페이서·페달·핸들 길이를 이 값으로 다시 계산함. 받으면 걸이 저울로 k 실측</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>지름 6</t>
+          <t>SUS304, 선경 1.5, 외경 18, 자유장 25 (스프링팜). 옵션 "수량: 1개"</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1082,189 +1082,189 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9638493021</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/4387963066</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>샤프트 칼라 Ø6 (무두볼트 고정)</t>
+          <t>압축 스프링 SUS304 (C147 대신)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>안 6 · 바깥 12 · 폭 6</t>
+          <t>선경 0.4 · 외경 5 · 자유장 10</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>레일 카트리지 6 + 여분 4</t>
+          <t>러그 디텐트 3 + 여분 3</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 RC 칼라는 해외배송 → 국내배송 칼라</t>
+          <t>판매 중인 기성품. 권수 약 6 → k 0.57 N/mm, 5mm 눌러 2.85N (C147 과 같은 범위), 밀착 2.4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>안지름 6, 바깥지름 12.5 이하, 폭 8 이하 (옵션 "SCC6 6-12-6")</t>
+          <t>선경 0.4, 외경 5, 자유장 10. 옵션 "스프링 0.4X5X10"</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://m.gmarket.co.kr/vi/product/4101441390</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8501265889</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="35" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>압축 스프링 (C252 대신, 기성품)</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>외경 17.0~18.5 · 안지름 12.8 이상 · 자유장 30~36 · 선경 1.5~1.7 · 밀착 높이 15 이하 · 권수가 보일 것</t>
+          <t>M3×8</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>변속기 9 (포크 카트리지 3 · 클러치 3 · 레버 후진 잠금 1 · 페달 복귀 2) + 핸들 복귀 2 + 여분 4</t>
+          <t>포크 카트리지 뚜껑 6 · 디텐트 3 + 여분 2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>판매 중인 기성품으로 (사용자 결정). 고른 스프링의 k·자유장으로 카트리지 길이·클러치 조절나사·페달 길이를 다시 계산</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>외경 17.0~18.5 · 안지름 12.8 이상 · 자유장 30~36 · 선경 1.5~1.7 · 밀착 높이 15 이하 · 권수가 보일 것</t>
+          <t>옵션 "M3 × 8mm"</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=압축스프링 외경18</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="35" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>압축 스프링 (C147 대신, 기성품)</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>외경 4.5~5.5 · 자유장 9~12 · 선경 0.4~0.5 · 밀착 높이 4.5 이하 · 권수가 보일 것</t>
+          <t>M3×10</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>러그 디텐트 3 + 여분 3</t>
+          <t>클러치 포크 속선 누름 1 + 여분 1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>판매 중인 기성품으로</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>외경 4.5~5.5 · 자유장 9~12 · 선경 0.4~0.5 · 밀착 높이 4.5 이하 · 권수가 보일 것</t>
+          <t>옵션 "M3 × 10mm"</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=스텐 압축스프링 선경0.5 외경5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/6455358137</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>M3×8</t>
+          <t>M3×12</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>포크 카트리지 뚜껑 6 · 디텐트 3 + 여분 2</t>
+          <t>칼라 7 · 클러치 덮개 7 · 축 끝 덮개 4 · 바퀴 덮개 2 · 아크릴 14 · 핸들 뒤 덮개 4 = 38 + 여분 6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두(둥근머리)</t>
+          <t>옵션 "M3 × 12mm"</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1284,35 +1284,35 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>M3×10</t>
+          <t>M3×16</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>클러치 포크 속선 누름 1 + 여분 1</t>
+          <t>바퀴 덮개 받침 2 + 여분 1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>옵션 "M3 × 16mm"</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1326,41 +1326,41 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="50" customHeight="1">
+    <row r="19" ht="35" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>M3×12</t>
+          <t>M3×20</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>칼라 7 · 클러치 덮개 7 · 축 끝 덮개 4 · 바퀴 덮개 2 · 아크릴 14 · 핸들 뒤 덮개 4 = 38 + 여분 6</t>
+          <t>슬리브 결합 9 + 여분 2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>핸들 4 · 여분 추가</t>
+          <t>볼트와 너트를 다른 줄로 (너트는 상품 번호가 다름)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>옵션 "M3 × 20mm"</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1380,35 +1380,35 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>M3×16</t>
+          <t>M3×25</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>바퀴 덮개 받침 2 + 여분 1</t>
+          <t>러그 6 + 여분 2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>M3×30 안 됨 (머리가 캐리어에 닿음)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 + 육각너트</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>M3×20</t>
+          <t>M3×50</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>슬리브 결합 9 + 여분 2</t>
+          <t>끝 채움판 4 + 여분 1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>볼트 70 + 스텐 육각너트 M3 60</t>
+          <t>옵션 "M3 × 50mm"</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1476,35 +1476,35 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>M3 육각너트 스텐</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>M3×25</t>
+          <t>M3 (맞변 5.5)</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>러그 6 + 여분 2</t>
+          <t>슬리브 결합 9 · 핸들 무두볼트 2 + 여분 4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>리우툴 너트 상품</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>M3×30 안 됨 (머리가 캐리어에 닿음)</t>
+          <t>맞변 5.5. 옵션 "스텐 육각너트 M3"</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8532240860</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트</t>
+          <t>M3 무두볼트 스텐 (오목끝)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>M3×50</t>
+          <t>M3×8</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>끝 채움판 4 + 여분 1</t>
+          <t>표시 바퀴 1 · 핸들 허브 1 · 캠 1 + 여분 2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>핸들 받침 v4.2 는 2개</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>오목끝(컵), 길이 8. 옵션 "M3 × 8mm"</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7974822838</t>
         </is>
       </c>
     </row>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>M3 무두볼트 (오목끝)</t>
+          <t>M3 평와셔 스텐</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>M3×8</t>
+          <t>바깥 8 × 두께 0.5</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>표시 바퀴 1 · 핸들 허브·캠·커플러 3 + 여분 2</t>
+          <t>아크릴 나사 밑 14 · 속선 누름 1 + 여분 5</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>핸들 3 · 여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>오목끝(컵), 길이 8</t>
+          <t>옵션 "1.스텐 평와셔 × M3x8x0.5T"</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7974822838</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>M3 육각너트 스텐</t>
+          <t>M4 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>M3 (맞변 5.5)</t>
+          <t>M4×16</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1633,22 +1633,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>핸들 무두볼트 3 + 여분 2</t>
+          <t>클러치 포크 브래킷 4 + 여분 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (핸들)</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>맞변 5.5</t>
+          <t>옵션 "M4 × 16mm"</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1668,35 +1668,35 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>M3 평와셔 스텐</t>
+          <t>M4 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>바깥 8 × 두께 0.5</t>
+          <t>M4×25</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>아크릴 나사 밑 14 · 속선 누름 1 + 여분 5</t>
+          <t>페달 발판 4 + 여분 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>"스텐 평와셔 M3x8x0.5T"</t>
+          <t>옵션 "M4 × 25mm"</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7440529428</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1716,35 +1716,35 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M4 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>M4×16</t>
+          <t>M4×30</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>클러치 포크 브래킷 4 + 여분 1</t>
+          <t>케이지 4 · 피벗 8 · 게이트 4 · 받침 브래킷 4 · 핸들 몸체 4 = 24 + 여분 3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>옵션 "M4 × 30mm"</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1764,35 +1764,35 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M4 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>M4×25</t>
+          <t>M4×60</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>페달 발판 4 + 여분 1</t>
+          <t>클러치 기둥 3 + 여분 1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>옵션 "M4 × 60mm"</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1812,35 +1812,35 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M4 육각너트 스텐</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>M4×30</t>
+          <t>M4 (맞변 7)</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>케이지 4 · 피벗 8 · 게이트 4 · 받침 브래킷 4 · 핸들 몸체 4 = 24 + 여분 3</t>
+          <t>M4 볼트마다 1개 (16: 5 · 25: 5 · 30: 27 · 60: 4)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>핸들 4 · 여분 추가</t>
+          <t>리우툴 너트 상품</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>옵션 "스텐 육각너트 M4"</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531939792</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 + 너트</t>
+          <t>M5 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>M4×60</t>
+          <t>M5×10</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1873,22 +1873,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>클러치 기둥 3 + 여분 1</t>
+          <t>클러치 조절나사 3 + 여분 1</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>M5×12 이상 금지 (클러치 토크 초과)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1908,35 +1908,35 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 너트</t>
+          <t>M5 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>M5×10</t>
+          <t>M5×20</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>클러치 조절나사 3 + 여분 1</t>
+          <t>클러치 릴리스 누름 3 · 핸들 고정 6 (PCD 70 6구멍 가정) + 여분 3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>M5×12 이상 금지 (클러치 토크 초과)</t>
+          <t>옵션 "M5 × 20mm"</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1956,35 +1956,35 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 너트</t>
+          <t>M5 육각너트 스텐</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>M5×20</t>
+          <t>M5 (맞변 8)</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>클러치 릴리스 누름 3 · 핸들 고정 6 (PCD 70 6구멍 가정) + 여분 3</t>
+          <t>M5×10 · M5×20 마다 1개 (4 + 12)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>핸들 6 · 여분 추가</t>
+          <t>리우툴 너트 상품</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두</t>
+          <t>옵션 "스텐 육각너트 M5"</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531595719</t>
         </is>
       </c>
     </row>
@@ -2004,20 +2004,20 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>M5 조정용 볼트 세트</t>
+          <t>M5 렌치볼트 스텐 (조정용)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>M5×8 3 + M5×12 3 + M5 평와셔 3</t>
+          <t>M5×8</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>클러치 토크 시험 3 결과로 조절나사 바꿈</t>
+          <t>클러치 토크 시험 3 에서 힘이 크면 조절나사를 이것으로</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2025,10 +2025,14 @@
           <t>그대로</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>옵션 "M5 × 8mm"</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2048,35 +2052,35 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 나일론 너트</t>
+          <t>M5 렌치볼트 스텐 (조정용)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>M5×70</t>
+          <t>M5×12</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>클러치 포크 피벗 1 + 여분 1</t>
+          <t>클러치 토크 시험 3 에서 힘이 작으면 이것 + 와셔 1장</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두 + 나일론 너트</t>
+          <t>옵션 "M5 × 12mm" (와셔 없이 쓰면 금지)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2096,12 +2100,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 + 나일론 너트</t>
+          <t>M5 평와셔 스텐</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>M5×40</t>
+          <t>바깥 12 × 두께 0.5</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -2109,22 +2113,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>핸들 롤러 팔 피벗 1 · 스프링 받침 1 + 여분 1</t>
+          <t>조정용 M5×12 밑</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (핸들)</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>스텐 유두 + 나일론 너트</t>
+          <t>옵션 "1.스텐 평와셔 × M5x12x0.5T"</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2134,7 +2138,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -2144,35 +2148,35 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M6 렌치볼트</t>
+          <t>M5 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>M6×25</t>
+          <t>M5×70</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>모터 받침 4 · 페달 피벗 2 + 여분 1</t>
+          <t>클러치 포크 피벗 1 + 여분 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>M6×30 이상 금지</t>
+          <t>옵션 "M5 × 70mm"</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2192,35 +2196,35 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>M6 너트</t>
+          <t>M5 나일론 너트 스텐</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>M6 (맞변 10)</t>
+          <t>M5 (DIN985)</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>모터 받침 4 + 여분 1</t>
+          <t>클러치 포크 피벗 1 + 여분 1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>리우툴 나일론 너트 상품</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>맞변 10</t>
+          <t>옵션 "스텐 나일론 너트 × M5"</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2230,7 +2234,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7687671245</t>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
       </c>
     </row>
@@ -2240,35 +2244,35 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>M6 나일론 너트</t>
+          <t>M6 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>M6 (DIN985)</t>
+          <t>M6×25</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>페달 피벗 2 + 여분 1</t>
+          <t>모터 받침 4 · 페달 피벗 2 + 여분 1</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>두께 6</t>
+          <t>M6×30 이상 금지</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2278,7 +2282,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6280971320</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -2288,35 +2292,35 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>목재 나사 스텐 둥근머리</t>
+          <t>M6 육각너트 스텐</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>4×16, 26개 봉</t>
+          <t>M6 (맞변 10)</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>받침 브래킷 8 · 클러치 덮개 4 · 모터 받침 4 · 페달 받침 8 = 24 + 여분</t>
+          <t>모터 받침 4 + 여분 1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1봉 → 2봉</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>옵션 "e)4x16mm-26개", 4×20 이상 안 됨</t>
+          <t>옵션 "스텐 육각너트 M6"</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2326,7 +2330,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7760964029</t>
+          <t>https://www.coupang.com/vp/products/7687671245</t>
         </is>
       </c>
     </row>
@@ -2336,45 +2340,45 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품</t>
+          <t>M6 나일론 너트 스텐</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2.85mm, 750g</t>
+          <t>M6 (DIN985)</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>출력 전체 4.66kg (핸들 받침 포함) + 실패 여유 15% = 5.36kg → 750g 8롤 (6kg)</t>
+          <t>페달 피벗 2 + 여분 1</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>따로 준비 → 신청 (지금 쓰는 것과 같은 제품: 쿠폰 공차가 그대로 맞음)</t>
+          <t>단가 170 → 70 (화면)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>UltiMaker 정품 PLA, 2.85mm, 750g, 국내배송 (색은 사용자에게)</t>
+          <t>옵션 "스텐 나일론 너트 × M6"</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 다른 세션 확인가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=울티메이커 PLA 2.85mm 750g</t>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2388,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2액형 에폭시 접착제</t>
+          <t>목재 나사 스텐 둥근머리</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>주사기형 25ml</t>
+          <t>4×16, 26개 봉</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2397,18 +2401,22 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항·롤러 핀</t>
+          <t>받침 브래킷 8 · 클러치 덮개 4 · 모터 받침 4 · 페달 받침 8 = 24 + 여분</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1 → 2 (쿠션 24개)</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>옵션 "e)4x16mm-26개", 4×20 이상 안 됨</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2418,41 +2426,45 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/2725054</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7760964029</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>순간접착제</t>
+          <t>PLA 필라멘트 울티메이커 정품 검정</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>젤 타입 2개</t>
+          <t>2.85mm, 750g</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>덮개 스위치·홀센서·자석</t>
+          <t>프레임 1.11kg · 핸들 받침 0.61kg (+15% 실패 여유 = 1.97kg)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>지금 쓰는 것과 같은 제품이라 쿠폰 공차가 그대로 맞음. 색은 기능별로 나눔 (검정 프레임 · 주황 기어 · 파랑 변속 · 노랑 클러치·페달). 흰색·회색은 쿠팡에 없음</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>UltiMaker PLA 2.85mm 750g, 옵션 "Black"</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2462,7 +2474,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8643897709</t>
+          <t>https://www.coupang.com/vp/products/9783043879</t>
         </is>
       </c>
     </row>
@@ -2472,35 +2484,35 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트</t>
+          <t>PLA 필라멘트 울티메이커 정품 주황</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>속선 2 + 아우터 Ø5 + 끝 캡</t>
+          <t>2.85mm, 750g</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
+          <t>기어 1.29kg (+15% = 1.48kg)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>같은 판매자, 색만 다름</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>아우터 바깥지름 5</t>
+          <t>옵션 "Orange"</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2510,45 +2522,45 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8305908512</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9783044238</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="35" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MDF 판</t>
+          <t>PLA 필라멘트 울티메이커 정품 파랑</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>12T 300×1200 재단</t>
+          <t>2.85mm, 750g</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>바닥판 750×300 + 페달 받침판 450×300</t>
+          <t>슬리브·변속 0.91kg · 축 부속·시험편 0.10kg (+15% = 1.17kg)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>같은 판매자, 색만 다름</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>두께 12</t>
+          <t>옵션 "Blue"</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2558,7 +2570,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/71452005</t>
+          <t>https://www.coupang.com/vp/products/9783043880</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2580,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단</t>
+          <t>PLA 필라멘트 울티메이커 정품 노랑</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>250×321</t>
+          <t>2.85mm, 750g</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -2581,95 +2593,95 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>덮개 윗판</t>
+          <t>클러치·페달 0.64kg (+15% = 0.74kg)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>A3 원판을 손으로 자르는 대신 치수 재단 (모서리 곧음)</t>
+          <t>같은 판매자, 색만 다름</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>두께 3, 투명, 옵션에 크기 입력 (구멍은 직접 Ø3.4)</t>
+          <t>옵션 "Yellow"</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9783043850</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="35" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단</t>
+          <t>2액형 에폭시 접착제</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>200×321</t>
+          <t>주사기형 25ml, 2개 묶음</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>덮개 옆판 2</t>
+          <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항 몸통·롤러 핀</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>1개씩 2번보다 2개 옵션이 1,250원 쌈</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>옵션 "2개"</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
+          <t>https://www.coupang.com/vp/products/2725054</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="35" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>투명 아크릴 A3 3T (여분)</t>
+          <t>순간접착제</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>297×420</t>
+          <t>젤 타입 2개</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2677,22 +2689,22 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>구멍 뚫다 깨질 때 바로 다시 자름</t>
+          <t>덮개 스위치·홀센서·자석</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>두께 3</t>
+          <t>옵션 "2개"</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2702,7 +2714,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9593337115</t>
+          <t>https://www.coupang.com/vp/products/8643897709</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2724,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>PTFE 합성 그리스 (슈퍼루브)</t>
+          <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>85g</t>
+          <t>속선 2 + 아우터 + 끝 캡</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2725,32 +2737,32 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>기어 이·슬리브 키·레일·핸들 캠</t>
+          <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>새로 추가: 플라스틱에 써도 되는 그리스 → 마모·소음 줄임</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>PTFE(테프론) 합성 그리스</t>
+          <t>아우터 바깥지름 화면 미표기 (자전거 표준 5) → 받으면 잼</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/5099555102</t>
+          <t>https://www.coupang.com/vp/products/8305908512</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2772,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>나사 고정제 록타이트 243</t>
+          <t>MDF 판</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>10ml</t>
+          <t>12T 300×1200 재단</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2773,47 +2785,47 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>금속끼리 나사: 칼라·핸들 무두볼트, 모터 M6</t>
+          <t>바닥판 750×300 + 페달 받침판 450×300</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>새로 추가: 모터 진동으로 풀림 방지 (PLA 에는 쓰지 않음)</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>243 (중강도, 분해 가능)</t>
+          <t>두께 12, 옵션 "06 MDF"</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/7426834008</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
+          <t>https://www.coupang.com/vp/products/71452005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="65" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>열수축 튜브 세트</t>
+          <t>투명 아크릴 3T 치수 재단</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>여러 지름 묶음</t>
+          <t>250×321</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -2821,87 +2833,95 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>홀센서·가변저항·스위치 납땜부 절연</t>
+          <t>덮개 윗판</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
+          <t>11번가 가격표 방식: 10cm 단위로 올린 30×40cm = 1,000원 × 6. 주문: 옵션 "3T / 투명 / 가공필요없음", 수량 6, 사이즈 칸에 250×321</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>두께 3, 투명 (구멍은 직접 Ø3.5)</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2070330612</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
+          <t>https://www.11st.co.kr/products/4918717495</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="35" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>케이블 타이</t>
+          <t>투명 아크릴 3T 치수 재단</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>100개</t>
+          <t>200×321</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
+          <t>덮개 옆판 2</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>같은 방식: 20×40cm = 1,000원 × 5. 주문: 장마다 수량 5, 사이즈 칸에 200×321</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>같음</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2283460419</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
+          <t>https://www.11st.co.kr/products/4918717495</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="35" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>신호선 22AWG 연선</t>
+          <t>투명 아크릴 A3 3T (여분)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6색, 색마다 5m</t>
+          <t>297×420</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2909,47 +2929,47 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>페달·핸들 가변저항, 홀센서 → 아두이노</t>
+          <t>구멍 뚫다 깨질 때 바로 다시 자름</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>m 단위 판매면 색마다 5m</t>
+          <t>옵션 "A3 투명 3T(기본사각)"</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/679503128</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9593337115</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="50" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스 150mm</t>
+          <t>PTFE 그리스 (슈퍼루브)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>0.01mm, 미쓰도요 500-196-30 또는 같은 급</t>
+          <t>85g</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2957,32 +2977,32 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>쿠폰 공차 · D컷 두 면 사이 10.00 · 가변저항·스프링·호스 실측</t>
+          <t>기어 이·슬리브 키·레일·핸들 캠</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (없음)</t>
+          <t>플라스틱에 써도 되는 테프론 그리스. 11번가 5099555102 는 실리콘 그리스라 바꿈</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>분해능 0.01mm, 150mm, 정품</t>
+          <t>PTFE(테프론) 합성 그리스</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=미쓰도요 디지털 캘리퍼스 500-196-30</t>
+          <t>https://www.coupang.com/vp/products/6071008034</t>
         </is>
       </c>
     </row>
@@ -2992,12 +3012,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>디지털 걸이 저울</t>
+          <t>나사 고정제 록타이트 243</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>최대 10kg 이상, 5g 단위 이하</t>
+          <t>10ml</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -3005,32 +3025,32 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>클러치 토크 시험 3 · 스프링 k 확인</t>
+          <t>금속끼리 나사: 칼라·핸들 무두볼트, 모터 M6 (마봉이 가늘면 끝판 베어링 자리)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (없음)</t>
+          <t>그대로 (단가 7,790 → 8,580)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>최대 10kg 이상, 눈금 5g 이하</t>
+          <t>243 (중강도, 분해 가능)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=디지털 걸이저울 10kg</t>
+          <t>https://www.11st.co.kr/products/7426834008</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3060,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>탁상 바이스</t>
+          <t>열수축 튜브 세트</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>조 폭 100mm (4인치), 작업대 고정</t>
+          <t>1~14mm 164개</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -3053,32 +3073,32 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>D컷 작업 때 축 고정 (조에 알루미늄판이나 두꺼운 종이를 댐)</t>
+          <t>홀센서·가변저항·스위치 납땜부 절연</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (없음)</t>
+          <t>전자부품을 동신전자 한 곳으로 묶음</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>조 폭 100mm 안팎</t>
+          <t>옵션 "(PP-K022) 열수축튜브 세트"</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=탁상 바이스 4인치</t>
+          <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
       </c>
     </row>
@@ -3088,12 +3108,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>철공용 평줄</t>
+          <t>케이블 타이</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>중목 250mm</t>
+          <t>100개, 흑색</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -3101,32 +3121,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>D컷 마무리 (그라인더 다음)</t>
+          <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (없음)</t>
+          <t>로켓배송 (11번가는 배송비 3,000)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>철공용, 평줄, 중목</t>
+          <t>옵션 "100개, 흑색"</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=철공용 평줄 중목 250mm</t>
+          <t>https://www.coupang.com/vp/products/8850608631</t>
         </is>
       </c>
     </row>
@@ -3136,141 +3156,141 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>철공용 평줄</t>
+          <t>신호선 0.3SQ (약 22AWG) 10색</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>세목 200mm</t>
+          <t>10색 × 1m 세트</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>D컷 마지막 0.05mm</t>
+          <t>페달·핸들 가변저항, 홀센서 → 아두이노 (5세트 = 색마다 5m)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (없음)</t>
+          <t>동신전자로 묶음</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>철공용, 평줄, 세목</t>
+          <t>옵션 "선택 01) 10색선 0.3SQ 1M"</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=철공용 평줄 세목 200mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9183828539</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>앵글 그라인더 플랩 디스크</t>
+          <t>디지털 캘리퍼스 미쓰도요 CD-15APX</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>4인치(100mm) #80</t>
+          <t>150mm, 0.01mm (500-196-30 신형)</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>D컷 거친 깎기 (숫돌보다 덜 파임)</t>
+          <t>쿠폰 공차 · D컷 두 면 사이 10.00 · 마봉·가변저항·스프링·호스 실측</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
+          <t>미쓰도요 정품 공식판매점(일본산). 3만원대 500-196-30 은 도착이 늦어 해외로 보고 뺌</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>지름 100, 구멍 16, #80</t>
+          <t>분해능 0.01mm, 150mm, 정품</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=플랩디스크 4인치 80방</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7773830124</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="50" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>앵글 그라인더 절단석</t>
+          <t>디지털 걸이 저울 레쿠</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>4인치(100mm) 두께 1mm</t>
+          <t>50kg × 10g</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>핸들 축 140 · 롤러 핀 · 여분 축 자르기</t>
+          <t>클러치 끌림·미끄럼 시험 (0.3~1.5kgf) · 스프링 k 실측 (약 3kg)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
+          <t>걸이형이면서 10kg 이상·5g 이하인 국내품이 없음 → 10g 단위로 충분 (가장 작은 측정 0.3kgf 에서 3%)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>지름 100, 구멍 16, 철재용</t>
+          <t>50kg × 10g, 전자식, 배터리 포함, 무료배송</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 브랜드관 검색 결과 2026-10-22 (상품 번호 미확인)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=절단석 4인치 1mm</t>
+          <t>https://www.coupang.com/np/products/brand-shop?brandName=레쿠</t>
         </is>
       </c>
     </row>
@@ -3280,41 +3300,45 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>보안경</t>
+          <t>탁상 바이스 ITL</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>투명, 측면 보호</t>
+          <t>조 폭 100mm, 360도 회전</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>그라인더 작업 (불티)</t>
+          <t>D컷 작업 때 축 고정 (조에 알루미늄판이나 두꺼운 종이를 댐)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
+          <t>주물, 클램프 고정</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>조 폭 100mm</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=보안경 측면보호</t>
+          <t>https://www.coupang.com/vp/products/8992172012</t>
         </is>
       </c>
     </row>
@@ -3324,41 +3348,45 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>절단 방지 장갑</t>
+          <t>철공용 평줄 중목</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>코팅</t>
+          <t>250mm</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>그라인더·줄 작업</t>
+          <t>D컷 마무리 (그라인더 다음)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>새로 추가</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
+          <t>이엑스파워 (로켓배송)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>철공용, 평줄, 중목</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=절단방지 장갑</t>
+          <t>https://www.coupang.com/vp/products/8997744652</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3396,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>HSS 드릴 날 세트</t>
+          <t>철공용 평줄 세목</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>19개 (1~10mm)</t>
+          <t>200mm</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3381,32 +3409,32 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>MDF 목재나사 밑구멍 Ø2.5, 아크릴 Ø3.4</t>
+          <t>D컷 마지막 0.05mm</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (보유한 것은 Ø3.4 하나)</t>
+          <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1~10mm 0.5 단위</t>
+          <t>철공용, 평줄, 세목</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2450926293</t>
+          <t>https://www.coupang.com/vp/products/8997744821</t>
         </is>
       </c>
     </row>
@@ -3416,45 +3444,45 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C클램프</t>
+          <t>플랩 디스크 100mm #80</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>4인치(100mm)</t>
+          <t>10개 봉</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>핸들 받침을 책상 모서리에 고정</t>
+          <t>D컷 거친 깎기 (3장 필요)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>새로 추가 (핸들)</t>
+          <t>디어포스 (로켓배송)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>벌어짐 60mm 이상, 목 깊이 60mm 이상</t>
+          <t>지름 100, #80, 구멍 16 (화면 미표기, 4인치 그라인더 가정)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=C클램프 4인치</t>
+          <t>https://www.coupang.com/vp/products/9416862249</t>
         </is>
       </c>
     </row>
@@ -3464,35 +3492,35 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + USB 케이블</t>
+          <t>절단석 105mm 두께 1mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ATmega32u4</t>
+          <t>5개 봉</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>게임 입력·모터 허가 1 + 여분 1</t>
+          <t>마봉 Ø12 · 스텐 Ø6 자르기 (9번 자름)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>여분 추가 (전시 중 고장 대비)</t>
+          <t>켈코 (4인치 그라인더용)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>레오나르도(32u4) — 우노 안 됨</t>
+          <t>지름 105, 두께 1, 철재용, 구멍 16 (화면 미표기)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3502,45 +3530,45 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/1119152790</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9375758010</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="35" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>홀센서 A3144</t>
+          <t>보안경 (측면 보호)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>3핀</t>
+          <t>투명</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
+          <t>그라인더 작업 (불티) · 2명</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>명신광학 J-67A 국산</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>A3144 (래치 아님)</t>
+          <t>옵션 "FREE × 투명"</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3550,7 +3578,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8520223332</t>
+          <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3588,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>네오디뮴 자석</t>
+          <t>절단 방지 장갑 NBR 코팅</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Ø6×3, 40개</t>
+          <t>L, 2개 묶음</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -3573,114 +3601,118 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>러그 3 · 표시 바퀴 4 + 여분</t>
+          <t>그라인더·줄 작업</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 10개 대신</t>
+          <t>한우 탑그립 CUT4 (로켓배송)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>지름 6 두께 3</t>
+          <t>옵션 "L × 2개"</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7119515778</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7759646279</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="35" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>가변저항 B10K (WH148 등 16mm)</t>
+          <t>HSS 드릴 날 세트</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>D축 Ø6 15mm, 부싱 M7, 3핀</t>
+          <t>19개 (1~10mm, 0.5 단위)</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
+          <t>MDF 목재나사 밑구멍 Ø2.5, 아크릴 Ø3.5</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 P160 대신 (국내배송)</t>
+          <t>보유한 것은 Ø3.4 하나</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>B10K, 몸통 Ø17.5 이하, 부싱 M7, 축 Ø6 길이 15 (장착면부터), D축(톱니 축이면 표시), 가운데 딸깍 없음</t>
+          <t>옵션 "상품02 하이스 드릴세트 19PCS"</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=가변저항 B10K 16mm D축 15mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
+          <t>https://www.11st.co.kr/products/2450926293</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="50" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>마이크로스위치 KW-11-3Z</t>
+          <t>C클램프 4인치</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>레버형</t>
+          <t>최대 벌림 105mm, 2개 묶음</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>덮개 열림 감지 1 + 여분 1</t>
+          <t>핸들 받침을 책상 모서리에 고정</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>엠케이</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>벌림 105 (받침판 8 + 책상 두께), 목 깊이 화면 미표기 (받침판 앞 끝에서 25mm 안을 물리므로 35 이상이면 됨)</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3690,41 +3722,45 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9167678186</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8261073812</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="35" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>점퍼 케이블 M-F</t>
+          <t>아두이노 레오나르도 R3 + USB 케이블</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>40P 40cm</t>
+          <t>ATmega32u4</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>센서 배선</t>
+          <t>게임 입력·모터 허가 1 + 여분 1</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
+          <t>전시 중 고장 대비 여분</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>레오나르도(32u4) — 우노 안 됨</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>v3 단가</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3734,7 +3770,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9699042565</t>
+          <t>https://www.coupang.com/vp/products/1119152790</t>
         </is>
       </c>
     </row>
@@ -3744,41 +3780,45 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>만능기판</t>
+          <t>홀센서 A3144</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>양면, 묶음</t>
+          <t>3핀</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>센서 배선 기판 (실수하면 새 판)</t>
+          <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 1장 대신</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>A3144 (래치 아님)</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9661304796</t>
+          <t>https://www.coupang.com/vp/products/8520223332</t>
         </is>
       </c>
     </row>
@@ -3788,35 +3828,35 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>자동차 릴레이 12V 40A + 소켓</t>
+          <t>네오디뮴 자석</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>4핀, 배선된 소켓</t>
+          <t>Ø6×3, 40개</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>모터 주 스위치 1 + 여분 1</t>
+          <t>러그 3 · 표시 바퀴 4 + 여분</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>여분 추가</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>코일 12V, 접점 30A 이상</t>
+          <t>지름 6 두께 3, 옵션 "40개입"</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3826,45 +3866,45 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6667848502</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7119515778</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="65" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
+          <t>가변저항 10K WH148 톱니 축</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>15A 포함, 홀더 4 + 퓨즈 12</t>
+          <t>16mm, 축 15mm, 부싱 M7, 3핀</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>배터리 + 단자 바로 옆</t>
+          <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>그대로 (여분 퓨즈 포함)</t>
+          <t>D(반달)축 국내품이 없어 톱니 축 → 페달 팔(80)·핸들 캠(93)의 축 구멍을 압입 구멍(POT_HOLE)으로 바꿈. B(직선형)·가운데 딸깍은 화면 미표기 → 받으면 확인</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>15A 퓨즈 포함</t>
+          <t>10K, 16mm, 축 15mm, 부싱 M7. 옵션 "가변저항 10K"</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3874,7 +3914,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9663070188</t>
+          <t>https://www.coupang.com/vp/products/8718871111</t>
         </is>
       </c>
     </row>
@@ -3884,45 +3924,41 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>비상정지 스위치 22mm</t>
+          <t>마이크로스위치 KW-11-3Z</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>버섯형, 1a1b, 명판 포함 (A20B-V4E11R)</t>
+          <t>레버형</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
+          <t>덮개 열림 감지 1 + 여분 1</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 KGE-C4R1R 대신</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>b접점(1b) 있음, 22mm</t>
-        </is>
-      </c>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://m.gmarket.co.kr/vi/product/711140155</t>
+          <t>https://www.coupang.com/vp/products/9167678186</t>
         </is>
       </c>
     </row>
@@ -3932,12 +3968,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>비상정지 스위치 박스</t>
+          <t>점퍼 케이블 F-M</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>1구 (22mm 구멍)</t>
+          <t>40P 40cm</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3945,32 +3981,32 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>비상정지 스위치를 넣어 운영자 앞 책상에 둠</t>
+          <t>센서 배선</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>새로 추가: 판에 구멍을 안 뚫어도 됨</t>
+          <t>동신전자로 묶음 (5,300 → 1,300)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1구, 구멍 22mm, 국내배송</t>
+          <t>옵션 "(PP-A848) 점퍼케이블 40핀 40cm 암/수"</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/8521960628</t>
+          <t>https://www.coupang.com/vp/products/9183828363</t>
         </is>
       </c>
     </row>
@@ -3980,12 +4016,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈 1채널</t>
+          <t>만능기판 양면 2.54</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>DM106</t>
+          <t>28×43홀 (약 71×109mm)</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -3993,32 +4029,32 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>아두이노 감시 → 주 릴레이 코일 차단 1 + 여분 1</t>
+          <t>센서 배선 기판 1 + 실수 대비 1</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 로우 트리거 모듈 대신</t>
+          <t>20장 묶음이 16,900 으로 올라 필요한 장수만</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>5V, 1채널 (하이/로우 트리거는 펌웨어로 맞춤)</t>
+          <t>옵션 "(PP-D021) 에폭시 양면기판 28x43"</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=1577801859</t>
+          <t>https://www.coupang.com/vp/products/9181560693</t>
         </is>
       </c>
     </row>
@@ -4028,45 +4064,45 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>다이오드 1N4007</t>
+          <t>자동차 릴레이 12V 40A + 소켓</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
+          <t>4핀, 배선된 소켓</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
+          <t>모터 주 스위치 1 + 여분 1</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 대신</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1N4007</t>
+          <t>코일 12V, 접점 30A 이상</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1453536560</t>
+          <t>https://www.coupang.com/vp/products/6667848502</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4112,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>저항 세트 1/4W</t>
+          <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>30종 × 20개 (10kΩ·4.7kΩ 포함)</t>
+          <t>15A 포함, 홀더 4 + 퓨즈 12</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -4089,32 +4125,32 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>안전 회로 감지 (비상정지·덮개 뒤 12V → 아두이노 A4)</t>
+          <t>배터리 + 단자 바로 옆</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>디바이스마트 2종 대신 세트</t>
+          <t>그대로 (여분 퓨즈 포함)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>10kΩ·4.7kΩ 들어 있을 것</t>
+          <t>15A 퓨즈 포함</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>검색 결과 2026-10-22 (화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1969785917</t>
+          <t>https://www.coupang.com/vp/products/9663070188</t>
         </is>
       </c>
     </row>
@@ -4124,35 +4160,35 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>실리콘 전선 16AWG 빨강·검정</t>
+          <t>비상정지 스위치 22mm + 1구 박스</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>1m 세트</t>
+          <t>LAS0-K-11TSA, 1a1b</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
+          <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2 → 3</t>
+          <t>G마켓 스위치 + 11번가 박스 대신 한 세트 (동신전자)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>16AWG 이상</t>
+          <t>b접점 있음 (1·2번 NC), 장착 Ø22.5, 박스 BXA-22/1/Y 포함. KC 미인증 표기</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4162,7 +4198,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7225302003</t>
+          <t>https://www.coupang.com/vp/products/9169916764</t>
         </is>
       </c>
     </row>
@@ -4172,35 +4208,35 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>절연 암 평형 단자 250 (6.3mm)</t>
+          <t>5V 릴레이 모듈 1채널 KY-019</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>22~16AWG, 2개 봉</t>
+          <t>1채널</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
+          <t>아두이노 감시 → 주 릴레이 코일 차단 1 + 여분 1</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>3 → 5</t>
+          <t>동신전자로 묶음</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>6.3mm 암, 절연형</t>
+          <t>5V, 1채널 (트리거 방식은 펌웨어로 맞춤)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4210,7 +4246,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8667960491</t>
+          <t>https://www.coupang.com/vp/products/9162331915</t>
         </is>
       </c>
     </row>
@@ -4220,12 +4256,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>배송비</t>
+          <t>다이오드 1N4007</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>판매처별 합계</t>
+          <t>10개</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -4233,28 +4269,268 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>판매처마다 3,000 안팎 (다른 세션에서 실제 값으로 바꿈)</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>하진전자로 묶음</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1N4007</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>예상단가: 쿠팡 화면 2026-10-20, 검색 결과 2026-10-22, 나머지는 추정. 상태가 "검색"·"찾기"인 줄은 쇼핑몰 화면에서 확인 후 확정 (쇼핑몰_확인_프롬프트.md). 모두 국내배송만. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더는 보유.</t>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9705767581</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="35" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>저항 1/4W 10kΩ</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>안전 회로 감지 분압 (12V → 아두이노 A4)</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>30종 세트 대신 필요한 값만</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>옵션 "10K"</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-22</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="35" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>저항 1/4W 4.7kΩ</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>10개</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>안전 회로 감지 분압</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>같은 상품의 다른 옵션</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>옵션 "4.7K"</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-22</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="35" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>실리콘 전선 16AWG 빨강·검정</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>1m 세트</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>그대로</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>16AWG 이상</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-22</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7225302003</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="35" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>절연 암 평형 단자 250 (6.3mm)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>10개 봉</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>동신전자로 묶음 (전과 같은 10개)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>6.3mm 암, 절연형 (전선 굵기 범위 화면 미표기)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-22</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9181548711</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="95" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>배송비</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>판매처별 합계</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>판매처 18곳 54,800 (다른 세션 화면 합계: 3,000 × 11 · 3,500 × 2 · 4,000 · 2,800 × 2 · 2,700 · 2,500) + G마켓 칼라 3,000 (추정). 로켓배송 11개(합계 77,320)와 무료배송 판매처는 0. 제주·도서산간 추가 제외</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-22</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>예상단가: 쿠팡·11번가 화면 2026-10-22 (다른 세션에서 확인). 상태가 "검색"인 2줄(칼라·걸이 저울)은 화면 미확인. 모두 국내배송. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더(4인치 가정)는 보유.</t>
         </is>
       </c>
     </row>

--- a/v4/물품계획서_근거.xlsx
+++ b/v4/물품계획서_근거.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -510,61 +510,61 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>볼 베어링 6001ZZ NSK</t>
+          <t>볼 베어링 6001ZZ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>12×28×8</t>
+          <t>12×28×8, 10개 묶음</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>변속기 19 (끝판 4 · 출력 기어 12 · 아이들러 2 · 클러치 파일럿 1) + 핸들 3 (축 2 · 롤러 1) + 여분 3</t>
+          <t>변속기 19 (끝판 4 · 출력 기어 12 · 아이들러 2 · 클러치 파일럿 1) + 핸들 3 (축 2 · 롤러 1) + 여분 8</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>NSK: 바깥지름 공차가 고르게 작아 쿠폰으로 정한 압입 구멍이 모두 맞고 소리가 작음. 11번가 2569692102 에는 6001 옵션이 없어 같은 판매자(소망트레이딩) 상품으로</t>
+          <t>값 낮춤: NSK 낱개 3,000원 × 25 → 일반 10개 묶음 (v3 에서 쓰던 상품). 압입 구멍은 00 쿠폰으로 이 베어링에 맞춤</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>NSK 6001ZZ, 12×28×8, 철판 실드(ZZ). 옵션 "NSK 6001 ZZ"</t>
+          <t>6001ZZ, 12×28×8, 철판 실드, 10개 묶음, 국내배송, 묶음 8,000원 이하</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-20 (국내배송 미확인)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1432577678</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8630678241</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>볼 베어링 6003ZZ NSK</t>
+          <t>볼 베어링 6003ZZ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -582,27 +582,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>같은 이유로 NSK (1번과 같은 상품)</t>
+          <t>값 낮춤: NSK 4,000원 → KYK (2026-10-20 화면)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>NSK 6003ZZ, 17×35×10. 옵션 "NSK 6003 ZZ"</t>
+          <t>6003ZZ, 17×35×10, 국내배송</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-20 (국내배송 미확인)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/1432577678</t>
+          <t>https://www.coupang.com/vp/products/8230435105</t>
         </is>
       </c>
     </row>
@@ -1005,11 +1005,11 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>레일 카트리지 6 + 여분 4</t>
+          <t>레일 카트리지 6 + 여분 2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>판매 중인 기성품 (사용자 결정). 사진으로 센 권수 5.5 → k ≈ 2.8 N/mm, 밀착 8.3. 자유장이 C252(32)보다 짧아 카트리지·클러치 컵·레버 스페이서·페달·핸들 길이를 이 값으로 다시 계산함. 받으면 걸이 저울로 k 실측</t>
+          <t>판매 중인 기성품 (사용자 결정). 사진으로 센 권수 5.5 → k ≈ 2.8 N/mm, 밀착 8.3. 자유장이 C252(32)보다 짧아 카트리지·클러치 컵·레버 스페이서·페달·핸들 길이를 이 값으로 다시 계산함. 받으면 물 무게로 k 실측 (설계서 10장)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2430,51 +2430,51 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="80" customHeight="1">
+    <row r="42" ht="95" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 검정</t>
+          <t>PLA 필라멘트 2.85mm 1kg 검정</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2.85mm, 750g</t>
+          <t>2.85mm, 1kg</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>프레임 1.11kg · 핸들 받침 0.61kg (+15% 실패 여유 = 1.97kg)</t>
+          <t>프레임 0.58 · 핸들 0.70 · 페달 0.44 · 축 부속·새 쿠폰 0.08kg (+15% 포함)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>지금 쓰는 것과 같은 제품이라 쿠폰 공차가 그대로 맞음. 색은 기능별로 나눔 (검정 프레임 · 주황 기어 · 파랑 변속 · 노랑 클러치·페달). 흰색·회색은 쿠팡에 없음</t>
+          <t>값 낮춤: 울티메이커 정품 750g 75,900원 × 8 → 일반 2.85mm 1kg × 5. 이미 뽑은 부품(출력 끝 0.17kg, print_next 0.90kg)은 뺌 → 남은 3.63kg + 15% = 4.17kg. 새 필라멘트로 00 쿠폰을 한 번 더 뽑아 공차를 정함</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>UltiMaker PLA 2.85mm 750g, 옵션 "Black"</t>
+          <t>PLA, 지름 2.85mm (허용차 ±0.05 이하 표기), 1kg, 국내배송, 1kg 40,000원 이하. 세 색 같은 브랜드</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783043879</t>
+          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 주황</t>
+          <t>PLA 필라멘트 2.85mm 1kg 주황</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2.85mm, 750g</t>
+          <t>2.85mm, 1kg</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2502,27 +2502,27 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>같은 판매자, 색만 다름</t>
+          <t>같은 브랜드, 색만 다름</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>옵션 "Orange"</t>
+          <t>위와 같음</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783044238</t>
+          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
         </is>
       </c>
     </row>
@@ -2532,45 +2532,45 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 파랑</t>
+          <t>PLA 필라멘트 2.85mm 1kg 파랑</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2.85mm, 750g</t>
+          <t>2.85mm, 1kg</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>슬리브·변속 0.91kg · 축 부속·시험편 0.10kg (+15% = 1.17kg)</t>
+          <t>슬리브·변속·클러치 0.78kg (+15% = 0.90kg)</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>같은 판매자, 색만 다름</t>
+          <t>같은 브랜드, 색만 다름</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>옵션 "Blue"</t>
+          <t>위와 같음</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783043880</t>
+          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 울티메이커 정품 노랑</t>
+          <t>2액형 에폭시 접착제</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2.85mm, 750g</t>
+          <t>주사기형 25ml, 2개 묶음</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>클러치·페달 0.64kg (+15% = 0.74kg)</t>
+          <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항 몸통·롤러 핀</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>같은 판매자, 색만 다름</t>
+          <t>1개씩 2번보다 2개 옵션이 1,250원 쌈</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>옵션 "Yellow"</t>
+          <t>옵션 "2개"</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9783043850</t>
+          <t>https://www.coupang.com/vp/products/2725054</t>
         </is>
       </c>
     </row>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2액형 에폭시 접착제</t>
+          <t>순간접착제</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>주사기형 25ml, 2개 묶음</t>
+          <t>젤 타입 2개</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항 몸통·롤러 핀</t>
+          <t>덮개 스위치·홀센서·자석</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1개씩 2번보다 2개 옵션이 1,250원 쌈</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/2725054</t>
+          <t>https://www.coupang.com/vp/products/8643897709</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>순간접착제</t>
+          <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>젤 타입 2개</t>
+          <t>속선 2 + 아우터 + 끝 캡</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>덮개 스위치·홀센서·자석</t>
+          <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>옵션 "2개"</t>
+          <t>아우터 바깥지름 화면 미표기 (자전거 표준 5) → 받으면 잼</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8643897709</t>
+          <t>https://www.coupang.com/vp/products/8305908512</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트</t>
+          <t>MDF 판</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>속선 2 + 아우터 + 끝 캡</t>
+          <t>12T 300×1200 재단</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
+          <t>바닥판 750×300 + 페달 받침판 450×300</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>아우터 바깥지름 화면 미표기 (자전거 표준 5) → 받으면 잼</t>
+          <t>두께 12, 옵션 "06 MDF"</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2762,22 +2762,22 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8305908512</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/71452005</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="65" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MDF 판</t>
+          <t>투명 아크릴 3T 치수 재단</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>12T 300×1200 재단</t>
+          <t>250×321</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2785,22 +2785,22 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>바닥판 750×300 + 페달 받침판 450×300</t>
+          <t>덮개 윗판</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>11번가 가격표 방식: 10cm 단위로 올린 30×40cm = 1,000원 × 6. 주문: 옵션 "3T / 투명 / 가공필요없음", 수량 6, 사이즈 칸에 250×321</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>두께 12, 옵션 "06 MDF"</t>
+          <t>두께 3, 투명 (구멍은 직접 Ø3.5)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2810,11 +2810,11 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/71452005</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="65" customHeight="1">
+          <t>https://www.11st.co.kr/products/4918717495</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="35" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -2825,25 +2825,25 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>250×321</t>
+          <t>200×321</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>덮개 윗판</t>
+          <t>덮개 옆판 2</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>11번가 가격표 방식: 10cm 단위로 올린 30×40cm = 1,000원 × 6. 주문: 옵션 "3T / 투명 / 가공필요없음", 수량 6, 사이즈 칸에 250×321</t>
+          <t>같은 방식: 20×40cm = 1,000원 × 5. 주문: 장마다 수량 5, 사이즈 칸에 200×321</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>두께 3, 투명 (구멍은 직접 Ø3.5)</t>
+          <t>같음</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2862,41 +2862,41 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="35" customHeight="1">
+    <row r="51" ht="50" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단</t>
+          <t>PTFE 그리스 (슈퍼루브)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>200×321</t>
+          <t>85g</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>덮개 옆판 2</t>
+          <t>기어 이·슬리브 키·레일·핸들 캠</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>같은 방식: 20×40cm = 1,000원 × 5. 주문: 장마다 수량 5, 사이즈 칸에 200×321</t>
+          <t>플라스틱에 써도 되는 테프론 그리스. 11번가 5099555102 는 실리콘 그리스라 바꿈</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>PTFE(테프론) 합성 그리스</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
+          <t>https://www.coupang.com/vp/products/6071008034</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>투명 아크릴 A3 3T (여분)</t>
+          <t>나사 고정제 록타이트 243</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>297×420</t>
+          <t>10ml</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>구멍 뚫다 깨질 때 바로 다시 자름</t>
+          <t>금속끼리 나사: 칼라·핸들 무두볼트, 모터 M6 (마봉이 가늘면 끝판 베어링 자리)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>그대로 (단가 7,790 → 8,580)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>옵션 "A3 투명 3T(기본사각)"</t>
+          <t>243 (중강도, 분해 가능)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>11번가 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2954,22 +2954,22 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9593337115</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="50" customHeight="1">
+          <t>https://www.11st.co.kr/products/7426834008</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="35" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PTFE 그리스 (슈퍼루브)</t>
+          <t>열수축 튜브 세트</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>85g</t>
+          <t>1~14mm 164개</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>기어 이·슬리브 키·레일·핸들 캠</t>
+          <t>홀센서·가변저항·스위치 납땜부 절연</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>플라스틱에 써도 되는 테프론 그리스. 11번가 5099555102 는 실리콘 그리스라 바꿈</t>
+          <t>전자부품을 동신전자 한 곳으로 묶음</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>PTFE(테프론) 합성 그리스</t>
+          <t>옵션 "(PP-K022) 열수축튜브 세트"</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6071008034</t>
+          <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>나사 고정제 록타이트 243</t>
+          <t>케이블 타이</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>10ml</t>
+          <t>100개, 흑색</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -3025,22 +3025,22 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>금속끼리 나사: 칼라·핸들 무두볼트, 모터 M6 (마봉이 가늘면 끝판 베어링 자리)</t>
+          <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>그대로 (단가 7,790 → 8,580)</t>
+          <t>로켓배송 (11번가는 배송비 3,000)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>243 (중강도, 분해 가능)</t>
+          <t>옵션 "100개, 흑색"</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/7426834008</t>
+          <t>https://www.coupang.com/vp/products/8850608631</t>
         </is>
       </c>
     </row>
@@ -3060,30 +3060,30 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>열수축 튜브 세트</t>
+          <t>신호선 0.3SQ (약 22AWG) 10색</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>1~14mm 164개</t>
+          <t>10색 × 1m 세트</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>홀센서·가변저항·스위치 납땜부 절연</t>
+          <t>페달·핸들 가변저항, 홀센서 → 아두이노 (5세트 = 색마다 5m)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>전자부품을 동신전자 한 곳으로 묶음</t>
+          <t>동신전자로 묶음</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>옵션 "(PP-K022) 열수축튜브 세트"</t>
+          <t>옵션 "선택 01) 10색선 0.3SQ 1M"</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3098,22 +3098,22 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828751</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9183828539</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="65" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>케이블 타이</t>
+          <t>디지털 캘리퍼스</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>100개, 흑색</t>
+          <t>150mm, 분해능 0.01mm</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
+          <t>쿠폰 공차 · D컷 두 면 사이 10.00 · 마봉·가변저항·스프링·호스 실측</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>로켓배송 (11번가는 배송비 3,000)</t>
+          <t>값 낮춤: 미쓰도요 156,400원 → 일반 디지털. 비교 측정(D컷 25mm 마다, 쿠폰)은 같은 캘리퍼스로 하므로 정확도 ±0.03 이면 충분</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>옵션 "100개, 흑색"</t>
+          <t>분해능 0.01mm, 150mm, 스텐 몸체, 국내배송, 30,000원 이하</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8850608631</t>
+          <t>https://www.coupang.com/np/search?q=디지털 캘리퍼스 150mm</t>
         </is>
       </c>
     </row>
@@ -3156,60 +3156,60 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>신호선 0.3SQ (약 22AWG) 10색</t>
+          <t>탁상 바이스</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>10색 × 1m 세트</t>
+          <t>조 폭 75~100mm, 책상에 클램프 고정</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>페달·핸들 가변저항, 홀센서 → 아두이노 (5세트 = 색마다 5m)</t>
+          <t>D컷 작업 때 축 고정 (조에 알루미늄판이나 두꺼운 종이를 댐)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>동신전자로 묶음</t>
+          <t>값 낮춤: ITL 34,900원 → 같은 크기 더 싼 것</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>옵션 "선택 01) 10색선 0.3SQ 1M"</t>
+          <t>주물, 조 폭 75mm 이상, 클램프로 책상 고정, 국내배송, 25,000원 이하</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828539</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="50" customHeight="1">
+          <t>https://www.coupang.com/np/search?q=탁상 바이스</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="35" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스 미쓰도요 CD-15APX</t>
+          <t>철공용 평줄 중목</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>150mm, 0.01mm (500-196-30 신형)</t>
+          <t>250mm</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -3217,17 +3217,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>쿠폰 공차 · D컷 두 면 사이 10.00 · 마봉·가변저항·스프링·호스 실측</t>
+          <t>D컷 마무리 (그라인더 다음)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>미쓰도요 정품 공식판매점(일본산). 3만원대 500-196-30 은 도착이 늦어 해외로 보고 뺌</t>
+          <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>분해능 0.01mm, 150mm, 정품</t>
+          <t>철공용, 평줄, 중목</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3242,22 +3242,22 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7773830124</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8997744652</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="35" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>디지털 걸이 저울 레쿠</t>
+          <t>철공용 평줄 세목</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>50kg × 10g</t>
+          <t>200mm</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -3265,32 +3265,32 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>클러치 끌림·미끄럼 시험 (0.3~1.5kgf) · 스프링 k 실측 (약 3kg)</t>
+          <t>D컷 마지막 0.05mm</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>걸이형이면서 10kg 이상·5g 이하인 국내품이 없음 → 10g 단위로 충분 (가장 작은 측정 0.3kgf 에서 3%)</t>
+          <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>50kg × 10g, 전자식, 배터리 포함, 무료배송</t>
+          <t>철공용, 평줄, 세목</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 브랜드관 검색 결과 2026-10-22 (상품 번호 미확인)</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/products/brand-shop?brandName=레쿠</t>
+          <t>https://www.coupang.com/vp/products/8997744821</t>
         </is>
       </c>
     </row>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>탁상 바이스 ITL</t>
+          <t>플랩 디스크 100mm #80</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>조 폭 100mm, 360도 회전</t>
+          <t>10개 봉</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>D컷 작업 때 축 고정 (조에 알루미늄판이나 두꺼운 종이를 댐)</t>
+          <t>D컷 거친 깎기 (3장 필요)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>주물, 클램프 고정</t>
+          <t>디어포스 (로켓배송)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>조 폭 100mm</t>
+          <t>지름 100, #80, 구멍 16 (화면 미표기, 4인치 그라인더 가정)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8992172012</t>
+          <t>https://www.coupang.com/vp/products/9416862249</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>철공용 평줄 중목</t>
+          <t>절단석 105mm 두께 1mm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>250mm</t>
+          <t>5개 봉</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3361,17 +3361,17 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>D컷 마무리 (그라인더 다음)</t>
+          <t>마봉 Ø12 · 스텐 Ø6 자르기 (9번 자름)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>이엑스파워 (로켓배송)</t>
+          <t>켈코 (4인치 그라인더용)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>철공용, 평줄, 중목</t>
+          <t>지름 105, 두께 1, 철재용, 구멍 16 (화면 미표기)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744652</t>
+          <t>https://www.coupang.com/vp/products/9375758010</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>철공용 평줄 세목</t>
+          <t>보안경 (측면 보호)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>200mm</t>
+          <t>투명</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>D컷 마지막 0.05mm</t>
+          <t>그라인더 작업 (불티, 작업하는 1명)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>이엑스파워 (로켓배송)</t>
+          <t>명신광학 J-67A 국산</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>철공용, 평줄, 세목</t>
+          <t>옵션 "FREE × 투명"</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744821</t>
+          <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>플랩 디스크 100mm #80</t>
+          <t>NBR 코팅 장갑</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>10개 봉</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3457,32 +3457,32 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>D컷 거친 깎기 (3장 필요)</t>
+          <t>그라인더·줄 작업</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>디어포스 (로켓배송)</t>
+          <t>값 낮춤: 절단 방지 장갑 2개 11,300원 → 일반 코팅 장갑</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>지름 100, #80, 구멍 16 (화면 미표기, 4인치 그라인더 가정)</t>
+          <t>NBR 코팅, L, 국내배송 (로켓배송이면 좋음), 5,000원 이하</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9416862249</t>
+          <t>https://www.coupang.com/np/search?q=NBR 코팅장갑</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>절단석 105mm 두께 1mm</t>
+          <t>HSS 드릴 날 2.5mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>5개 봉</t>
+          <t>1개</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -3505,65 +3505,65 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>마봉 Ø12 · 스텐 Ø6 자르기 (9번 자름)</t>
+          <t>MDF 목재나사 밑구멍 Ø2.5 (아크릴 Ø3.4 는 보유)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>켈코 (4인치 그라인더용)</t>
+          <t>값 낮춤: 19개 세트 7,740원 + 배송비 → 필요한 2.5mm 하나</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>지름 105, 두께 1, 철재용, 구멍 16 (화면 미표기)</t>
+          <t>HSS, 지름 2.5mm, 국내배송 (로켓배송이면 좋음), 3,000원 이하</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>찾기</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9375758010</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="35" customHeight="1">
+          <t>https://www.coupang.com/np/search?q=HSS 드릴날 2.5mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="50" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>보안경 (측면 보호)</t>
+          <t>C클램프 4인치</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>투명</t>
+          <t>최대 벌림 105mm, 2개 묶음</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>그라인더 작업 (불티) · 2명</t>
+          <t>핸들 받침을 책상 모서리에 고정</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>명신광학 J-67A 국산</t>
+          <t>엠케이</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>옵션 "FREE × 투명"</t>
+          <t>벌림 105 (받침판 8 + 책상 두께), 목 깊이 화면 미표기 (받침판 앞 끝에서 25mm 안을 물리므로 35 이상이면 됨)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8800840444</t>
+          <t>https://www.coupang.com/vp/products/8261073812</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>절단 방지 장갑 NBR 코팅</t>
+          <t>아두이노 레오나르도 R3 + USB 케이블</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>L, 2개 묶음</t>
+          <t>ATmega32u4</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>그라인더·줄 작업</t>
+          <t>게임 입력·모터 허가</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>한우 탑그립 CUT4 (로켓배송)</t>
+          <t>값 낮춤: 여분 뺌</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>옵션 "L × 2개"</t>
+          <t>레오나르도(32u4) — 우노 안 됨</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7759646279</t>
+          <t>https://www.coupang.com/vp/products/1119152790</t>
         </is>
       </c>
     </row>
@@ -3636,35 +3636,35 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>HSS 드릴 날 세트</t>
+          <t>홀센서 A3144</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>19개 (1~10mm, 0.5 단위)</t>
+          <t>3핀</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>MDF 목재나사 밑구멍 Ø2.5, 아크릴 Ø3.5</t>
+          <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>보유한 것은 Ø3.4 하나</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>옵션 "상품02 하이스 드릴세트 19PCS"</t>
+          <t>A3144 (래치 아님)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-22</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/2450926293</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8520223332</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="35" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C클램프 4인치</t>
+          <t>네오디뮴 자석</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>최대 벌림 105mm, 2개 묶음</t>
+          <t>Ø6×3, 40개</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
@@ -3697,17 +3697,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>핸들 받침을 책상 모서리에 고정</t>
+          <t>러그 3 · 표시 바퀴 4 + 여분</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>엠케이</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>벌림 105 (받침판 8 + 책상 두께), 목 깊이 화면 미표기 (받침판 앞 끝에서 25mm 안을 물리므로 35 이상이면 됨)</t>
+          <t>지름 6 두께 3, 옵션 "40개입"</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3722,40 +3722,40 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8261073812</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7119515778</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="65" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + USB 케이블</t>
+          <t>가변저항 10K WH148 톱니 축</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ATmega32u4</t>
+          <t>16mm, 축 15mm, 부싱 M7, 3핀</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>게임 입력·모터 허가 1 + 여분 1</t>
+          <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>전시 중 고장 대비 여분</t>
+          <t>D(반달)축 국내품이 없어 톱니 축 → 페달 팔(80)·핸들 캠(93)의 축 구멍을 압입 구멍(POT_HOLE)으로 바꿈. B(직선형)·가운데 딸깍은 화면 미표기 → 받으면 확인</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>레오나르도(32u4) — 우노 안 됨</t>
+          <t>10K, 16mm, 축 15mm, 부싱 M7. 옵션 "가변저항 10K"</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/1119152790</t>
+          <t>https://www.coupang.com/vp/products/8718871111</t>
         </is>
       </c>
     </row>
@@ -3780,20 +3780,20 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>홀센서 A3144</t>
+          <t>마이크로스위치 KW-11-3Z</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>3핀</t>
+          <t>레버형</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
+          <t>덮개 열림 감지 1 + 여분 1</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3801,11 +3801,7 @@
           <t>그대로</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>A3144 (래치 아님)</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>쿠팡 화면 2026-10-22</t>
@@ -3818,7 +3814,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8520223332</t>
+          <t>https://www.coupang.com/vp/products/9167678186</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3824,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>네오디뮴 자석</t>
+          <t>점퍼 케이블 F-M</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ø6×3, 40개</t>
+          <t>40P 40cm</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -3841,17 +3837,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>러그 3 · 표시 바퀴 4 + 여분</t>
+          <t>센서 배선</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>동신전자로 묶음 (5,300 → 1,300)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>지름 6 두께 3, 옵션 "40개입"</t>
+          <t>옵션 "(PP-A848) 점퍼케이블 40핀 40cm 암/수"</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3866,40 +3862,40 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7119515778</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="65" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9183828363</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="35" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>가변저항 10K WH148 톱니 축</t>
+          <t>만능기판 양면 2.54</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>16mm, 축 15mm, 부싱 M7, 3핀</t>
+          <t>28×43홀 (약 71×109mm)</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
+          <t>센서 배선 기판</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>D(반달)축 국내품이 없어 톱니 축 → 페달 팔(80)·핸들 캠(93)의 축 구멍을 압입 구멍(POT_HOLE)으로 바꿈. B(직선형)·가운데 딸깍은 화면 미표기 → 받으면 확인</t>
+          <t>20장 묶음이 16,900 으로 올라 필요한 장수만</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>10K, 16mm, 축 15mm, 부싱 M7. 옵션 "가변저항 10K"</t>
+          <t>옵션 "(PP-D021) 에폭시 양면기판 28x43"</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3914,7 +3910,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8718871111</t>
+          <t>https://www.coupang.com/vp/products/9181560693</t>
         </is>
       </c>
     </row>
@@ -3924,28 +3920,32 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>마이크로스위치 KW-11-3Z</t>
+          <t>자동차 릴레이 12V 40A + 소켓</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>레버형</t>
+          <t>4핀, 배선된 소켓</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>덮개 열림 감지 1 + 여분 1</t>
+          <t>모터 주 스위치</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>값 낮춤: 여분 뺌</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>코일 12V, 접점 30A 이상</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>쿠팡 화면 2026-10-22</t>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9167678186</t>
+          <t>https://www.coupang.com/vp/products/6667848502</t>
         </is>
       </c>
     </row>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>점퍼 케이블 F-M</t>
+          <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>40P 40cm</t>
+          <t>15A 포함, 홀더 4 + 퓨즈 12</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3981,17 +3981,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>센서 배선</t>
+          <t>배터리 + 단자 바로 옆</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>동신전자로 묶음 (5,300 → 1,300)</t>
+          <t>그대로 (여분 퓨즈 포함)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>옵션 "(PP-A848) 점퍼케이블 40핀 40cm 암/수"</t>
+          <t>15A 퓨즈 포함</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828363</t>
+          <t>https://www.coupang.com/vp/products/9663070188</t>
         </is>
       </c>
     </row>
@@ -4016,30 +4016,30 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>만능기판 양면 2.54</t>
+          <t>비상정지 스위치 22mm + 1구 박스</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>28×43홀 (약 71×109mm)</t>
+          <t>LAS0-K-11TSA, 1a1b</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>센서 배선 기판 1 + 실수 대비 1</t>
+          <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>20장 묶음이 16,900 으로 올라 필요한 장수만</t>
+          <t>G마켓 스위치 + 11번가 박스 대신 한 세트 (동신전자)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>옵션 "(PP-D021) 에폭시 양면기판 28x43"</t>
+          <t>b접점 있음 (1·2번 NC), 장착 Ø22.5, 박스 BXA-22/1/Y 포함. KC 미인증 표기</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9181560693</t>
+          <t>https://www.coupang.com/vp/products/9169916764</t>
         </is>
       </c>
     </row>
@@ -4064,30 +4064,30 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>자동차 릴레이 12V 40A + 소켓</t>
+          <t>5V 릴레이 모듈 1채널 KY-019</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>4핀, 배선된 소켓</t>
+          <t>1채널</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>모터 주 스위치 1 + 여분 1</t>
+          <t>아두이노 감시 → 주 릴레이 코일 차단</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>동신전자로 묶음</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>코일 12V, 접점 30A 이상</t>
+          <t>5V, 1채널 (트리거 방식은 펌웨어로 맞춤)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6667848502</t>
+          <t>https://www.coupang.com/vp/products/9162331915</t>
         </is>
       </c>
     </row>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
+          <t>다이오드 1N4007</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>15A 포함, 홀더 4 + 퓨즈 12</t>
+          <t>10개</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>배터리 + 단자 바로 옆</t>
+          <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>그대로 (여분 퓨즈 포함)</t>
+          <t>하진전자로 묶음</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>15A 퓨즈 포함</t>
+          <t>1N4007</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9663070188</t>
+          <t>https://www.coupang.com/vp/products/9705767581</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>비상정지 스위치 22mm + 1구 박스</t>
+          <t>저항 1/4W 10kΩ</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>LAS0-K-11TSA, 1a1b</t>
+          <t>10개</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
@@ -4173,17 +4173,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
+          <t>안전 회로 감지 분압 (12V → 아두이노 A4)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>G마켓 스위치 + 11번가 박스 대신 한 세트 (동신전자)</t>
+          <t>30종 세트 대신 필요한 값만</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>b접점 있음 (1·2번 NC), 장착 Ø22.5, 박스 BXA-22/1/Y 포함. KC 미인증 표기</t>
+          <t>옵션 "10K"</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9169916764</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -4208,30 +4208,30 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈 1채널 KY-019</t>
+          <t>저항 1/4W 4.7kΩ</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>1채널</t>
+          <t>10개</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>아두이노 감시 → 주 릴레이 코일 차단 1 + 여분 1</t>
+          <t>안전 회로 감지 분압</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>동신전자로 묶음</t>
+          <t>같은 상품의 다른 옵션</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>5V, 1채널 (트리거 방식은 펌웨어로 맞춤)</t>
+          <t>옵션 "4.7K"</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9162331915</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -4256,30 +4256,30 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>다이오드 1N4007</t>
+          <t>실리콘 전선 16AWG 빨강·검정</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
+          <t>1m 세트</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
+          <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>하진전자로 묶음</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1N4007</t>
+          <t>16AWG 이상</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9705767581</t>
+          <t>https://www.coupang.com/vp/products/7225302003</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>저항 1/4W 10kΩ</t>
+          <t>절연 암 평형 단자 250 (6.3mm)</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
+          <t>10개 봉</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -4317,17 +4317,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>안전 회로 감지 분압 (12V → 아두이노 A4)</t>
+          <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>30종 세트 대신 필요한 값만</t>
+          <t>동신전자로 묶음 (전과 같은 10개)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>옵션 "10K"</t>
+          <t>6.3mm 암, 절연형 (전선 굵기 범위 화면 미표기)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9181548711</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="95" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>저항 1/4W 4.7kΩ</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
+          <t>판매처별 합계</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
@@ -4365,172 +4365,28 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>안전 회로 감지 분압</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>같은 상품의 다른 옵션</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>옵션 "4.7K"</t>
-        </is>
-      </c>
+          <t>판매처 18곳 54,800 (2026-10-22 화면 합계) − 소망트레이딩(베어링)·공구랜드(드릴) + 베어링 판매처 2곳·G마켓 칼라 3,000씩 (추정). 새로 고르는 줄은 로켓배송(19,800 이상 무료)이나 이미 있는 판매자로 고르면 늘지 않음</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="35" customHeight="1">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>실리콘 전선 16AWG 빨강·검정</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>1m 세트</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>16AWG 이상</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-22</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/7225302003</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="35" customHeight="1">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>절연 암 평형 단자 250 (6.3mm)</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>10개 봉</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>동신전자로 묶음 (전과 같은 10개)</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>6.3mm 암, 절연형 (전선 굵기 범위 화면 미표기)</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-22</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/9181548711</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="95" customHeight="1">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>판매처별 합계</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>판매처 18곳 54,800 (다른 세션 화면 합계: 3,000 × 11 · 3,500 × 2 · 4,000 · 2,800 × 2 · 2,700 · 2,500) + G마켓 칼라 3,000 (추정). 로켓배송 11개(합계 77,320)와 무료배송 판매처는 0. 제주·도서산간 추가 제외</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-22</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>예상단가: 쿠팡·11번가 화면 2026-10-22 (다른 세션에서 확인). 상태가 "검색"인 2줄(칼라·걸이 저울)은 화면 미확인. 모두 국내배송. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더(4인치 가정)는 보유.</t>
+          <t>찾기</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>예상단가: 쿠팡·11번가 화면 2026-10-22 (다른 세션에서 확인). 상태 "검색"은 화면 확인 필요, "찾기"는 값을 낮추려고 새로 고를 줄 (단가는 추정, 상한 가격은 "꼭 맞아야 할 것" 칸). 모두 국내배송. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더(4인치 가정)는 보유.</t>
         </is>
       </c>
     </row>

--- a/v4/물품계획서_근거.xlsx
+++ b/v4/물품계획서_근거.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -534,22 +534,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: NSK 낱개 3,000원 × 25 → 일반 10개 묶음 (v3 에서 쓰던 상품). 압입 구멍은 00 쿠폰으로 이 베어링에 맞춤</t>
+          <t>값 낮춤: NSK 낱개 3,000원 × 25 → 일반 10개 묶음 (디오상공사, 무료배송). 압입 구멍은 00 쿠폰으로 이 베어링에 맞춤</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>6001ZZ, 12×28×8, 철판 실드, 10개 묶음, 국내배송, 묶음 8,000원 이하</t>
+          <t>6001ZZ, 12×28×8, 철판 실드. 옵션 "6001ZZ - 가성비 × 10개"</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20 (국내배송 미확인)</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>볼 베어링 6003ZZ</t>
+          <t>볼 베어링 6003ZZ KYK</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -582,22 +582,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: NSK 4,000원 → KYK (2026-10-20 화면)</t>
+          <t>값 낮춤: NSK 4,000원 → KYK (나라기업). 6001 판매자의 10개 묶음(7,000)보다 2개 + 배송비가 1,800원 쌈</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>6003ZZ, 17×35×10, 국내배송</t>
+          <t>6003ZZ, 17×35×10. 옵션 "수량: 1개"</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-20 (국내배송 미확인)</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -990,89 +990,89 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12" ht="95" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>샤프트 칼라 Ø6 (무두볼트 고정)</t>
+          <t>압축 스프링 SUS304 (C252 대신)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안 6 · 바깥 12 · 폭 6</t>
+          <t>선경 1.5 · 외경 18 · 자유장 25</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>레일 카트리지 6 + 여분 2</t>
+          <t>변속기 9 (포크 카트리지 3 · 클러치 3 · 레버 후진 잠금 1 · 페달 복귀 2) + 핸들 복귀 2 + 여분 4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 SCC6 은 모두 해외배송, 11번가는 국내 상품 없음 → G마켓 국내 상품 (검색 결과에 "국내배송만 가능"). G마켓 화면은 이 환경·다른 세션 모두 못 열어 사용자가 확인</t>
+          <t>판매 중인 기성품 (사용자 결정). 사진으로 센 권수 5.5 → k ≈ 2.8 N/mm, 밀착 8.3. 자유장이 C252(32)보다 짧아 카트리지·클러치 컵·레버 스페이서·페달·핸들 길이를 이 값으로 다시 계산함. 받으면 물 무게로 k 실측 (설계서 10장)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>안지름 6, 바깥지름 12.5 이하 (카트리지 구멍 13), 폭 8 이하, 강철, 국내배송. 옵션 "SCC6 6-12-6"</t>
+          <t>SUS304, 선경 1.5, 외경 18, 자유장 25 (스프링팜). 옵션 "수량: 1개"</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>추정 (G마켓 화면 미확인)</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://item.gmarket.co.kr/Item?goodscode=4101441390</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="95" customHeight="1">
+          <t>https://www.coupang.com/vp/products/4387963066</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>압축 스프링 SUS304 (C252 대신)</t>
+          <t>압축 스프링 SUS304 (C147 대신)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>선경 1.5 · 외경 18 · 자유장 25</t>
+          <t>선경 0.4 · 외경 5 · 자유장 10</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>변속기 9 (포크 카트리지 3 · 클러치 3 · 레버 후진 잠금 1 · 페달 복귀 2) + 핸들 복귀 2 + 여분 4</t>
+          <t>러그 디텐트 3 + 여분 3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>판매 중인 기성품 (사용자 결정). 사진으로 센 권수 5.5 → k ≈ 2.8 N/mm, 밀착 8.3. 자유장이 C252(32)보다 짧아 카트리지·클러치 컵·레버 스페이서·페달·핸들 길이를 이 값으로 다시 계산함. 받으면 물 무게로 k 실측 (설계서 10장)</t>
+          <t>판매 중인 기성품. 권수 약 6 → k 0.57 N/mm, 5mm 눌러 2.85N (C147 과 같은 범위), 밀착 2.4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>SUS304, 선경 1.5, 외경 18, 자유장 25 (스프링팜). 옵션 "수량: 1개"</t>
+          <t>선경 0.4, 외경 5, 자유장 10. 옵션 "스프링 0.4X5X10"</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1082,45 +1082,45 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/4387963066</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8501265889</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="35" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>압축 스프링 SUS304 (C147 대신)</t>
+          <t>M3 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>선경 0.4 · 외경 5 · 자유장 10</t>
+          <t>M3×8</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>러그 디텐트 3 + 여분 3</t>
+          <t>포크 카트리지 뚜껑 6 · 디텐트 3 + 여분 2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>판매 중인 기성품. 권수 약 6 → k 0.57 N/mm, 5mm 눌러 2.85N (C147 과 같은 범위), 밀착 2.4</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>선경 0.4, 외경 5, 자유장 10. 옵션 "스프링 0.4X5X10"</t>
+          <t>옵션 "M3 × 8mm"</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8501265889</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1145,30 +1145,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>M3×8</t>
+          <t>M3×10</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>포크 카트리지 뚜껑 6 · 디텐트 3 + 여분 2</t>
+          <t>클러치 포크 속선 누름 1 · 출력 레일 칼라 조임 6 + 여분 3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>레일 칼라를 출력으로 바꿔 6개 추가 (국내배송 칼라 판매 종료)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M3 × 8mm"</t>
+          <t>옵션 "M3 × 10mm"</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="35" customHeight="1">
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1193,15 +1193,15 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>M3×10</t>
+          <t>M3×12</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>클러치 포크 속선 누름 1 + 여분 1</t>
+          <t>칼라 7 · 클러치 덮개 7 · 축 끝 덮개 4 · 바퀴 덮개 2 · 아크릴 14 · 핸들 뒤 덮개 4 = 38 + 여분 6</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M3 × 10mm"</t>
+          <t>옵션 "M3 × 12mm"</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="50" customHeight="1">
+    <row r="17" ht="35" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1241,15 +1241,15 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>M3×12</t>
+          <t>M3×16</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>칼라 7 · 클러치 덮개 7 · 축 끝 덮개 4 · 바퀴 덮개 2 · 아크릴 14 · 핸들 뒤 덮개 4 = 38 + 여분 6</t>
+          <t>바퀴 덮개 받침 2 + 여분 1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M3 × 12mm"</t>
+          <t>옵션 "M3 × 16mm"</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1289,30 +1289,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>M3×16</t>
+          <t>M3×20</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>바퀴 덮개 받침 2 + 여분 1</t>
+          <t>슬리브 결합 9 + 여분 2</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>볼트와 너트를 다른 줄로 (너트는 상품 번호가 다름)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M3 × 16mm"</t>
+          <t>옵션 "M3 × 20mm"</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1337,30 +1337,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>M3×20</t>
+          <t>M3×25</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>슬리브 결합 9 + 여분 2</t>
+          <t>러그 6 + 여분 2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>볼트와 너트를 다른 줄로 (너트는 상품 번호가 다름)</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M3 × 20mm"</t>
+          <t>M3×30 안 됨 (머리가 캐리어에 닿음)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1385,15 +1385,15 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>M3×25</t>
+          <t>M3×50</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>러그 6 + 여분 2</t>
+          <t>끝 채움판 4 + 여분 1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>M3×30 안 됨 (머리가 캐리어에 닿음)</t>
+          <t>옵션 "M3 × 50mm"</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>M3 렌치볼트 스텐</t>
+          <t>M3 육각너트 스텐</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>M3×50</t>
+          <t>M3 (맞변 5.5)</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>끝 채움판 4 + 여분 1</t>
+          <t>슬리브 결합 9 · 핸들 무두볼트 2 + 여분 4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>리우툴 너트 상품</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M3 × 50mm"</t>
+          <t>맞변 5.5. 옵션 "스텐 육각너트 M3"</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8532240860</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1476,35 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>M3 육각너트 스텐</t>
+          <t>M3 무두볼트 스텐 (오목끝)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>M3 (맞변 5.5)</t>
+          <t>M3×8</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>슬리브 결합 9 · 핸들 무두볼트 2 + 여분 4</t>
+          <t>표시 바퀴 1 · 핸들 허브 1 · 캠 1 + 여분 2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>리우툴 너트 상품</t>
+          <t>핸들 받침 v4.2 는 2개</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>맞변 5.5. 옵션 "스텐 육각너트 M3"</t>
+          <t>오목끝(컵), 길이 8. 옵션 "M3 × 8mm"</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8532240860</t>
+          <t>https://www.coupang.com/vp/products/7974822838</t>
         </is>
       </c>
     </row>
@@ -1524,35 +1524,35 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>M3 무두볼트 스텐 (오목끝)</t>
+          <t>M3 평와셔 스텐</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>M3×8</t>
+          <t>바깥 8 × 두께 0.5</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>표시 바퀴 1 · 핸들 허브 1 · 캠 1 + 여분 2</t>
+          <t>아크릴 나사 밑 14 · 속선 누름 1 + 여분 5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>핸들 받침 v4.2 는 2개</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>오목끝(컵), 길이 8. 옵션 "M3 × 8mm"</t>
+          <t>옵션 "1.스텐 평와셔 × M3x8x0.5T"</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7974822838</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -1572,35 +1572,35 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>M3 평와셔 스텐</t>
+          <t>M4 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>바깥 8 × 두께 0.5</t>
+          <t>M4×16</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>아크릴 나사 밑 14 · 속선 누름 1 + 여분 5</t>
+          <t>클러치 포크 브래킷 4 + 여분 1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>옵션 "1.스텐 평와셔 × M3x8x0.5T"</t>
+          <t>옵션 "M4 × 16mm"</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7440529428</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>M4×16</t>
+          <t>M4×25</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>클러치 포크 브래킷 4 + 여분 1</t>
+          <t>페달 발판 4 + 여분 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M4 × 16mm"</t>
+          <t>옵션 "M4 × 25mm"</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1673,15 +1673,15 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>M4×25</t>
+          <t>M4×30</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>페달 발판 4 + 여분 1</t>
+          <t>케이지 4 · 피벗 8 · 게이트 4 · 받침 브래킷 4 · 핸들 몸체 4 = 24 + 여분 3</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M4 × 25mm"</t>
+          <t>옵션 "M4 × 30mm"</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1721,15 +1721,15 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>M4×30</t>
+          <t>M4×60</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>케이지 4 · 피벗 8 · 게이트 4 · 받침 브래킷 4 · 핸들 몸체 4 = 24 + 여분 3</t>
+          <t>클러치 기둥 3 + 여분 1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M4 × 30mm"</t>
+          <t>옵션 "M4 × 60mm"</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1764,35 +1764,35 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>M4 렌치볼트 스텐</t>
+          <t>M4 육각너트 스텐</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>M4×60</t>
+          <t>M4 (맞변 7)</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>클러치 기둥 3 + 여분 1</t>
+          <t>M4 볼트마다 1개 (16: 5 · 25: 5 · 30: 27 · 60: 4)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>볼트와 너트를 다른 줄로</t>
+          <t>리우툴 너트 상품</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M4 × 60mm"</t>
+          <t>옵션 "스텐 육각너트 M4"</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531939792</t>
         </is>
       </c>
     </row>
@@ -1812,35 +1812,35 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>M4 육각너트 스텐</t>
+          <t>M5 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>M4 (맞변 7)</t>
+          <t>M5×10</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>M4 볼트마다 1개 (16: 5 · 25: 5 · 30: 27 · 60: 4)</t>
+          <t>클러치 조절나사 3 + 여분 1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>리우툴 너트 상품</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>옵션 "스텐 육각너트 M4"</t>
+          <t>M5×12 이상 금지 (클러치 토크 초과)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8531939792</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -1865,15 +1865,15 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>M5×10</t>
+          <t>M5×20</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>클러치 조절나사 3 + 여분 1</t>
+          <t>클러치 릴리스 누름 3 · 핸들 고정 6 (PCD 70 6구멍 가정) + 여분 3</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>M5×12 이상 금지 (클러치 토크 초과)</t>
+          <t>옵션 "M5 × 20mm"</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1908,35 +1908,35 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐</t>
+          <t>M5 육각너트 스텐</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>M5×20</t>
+          <t>M5 (맞변 8)</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>클러치 릴리스 누름 3 · 핸들 고정 6 (PCD 70 6구멍 가정) + 여분 3</t>
+          <t>M5×10 · M5×20 마다 1개 (4 + 12)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>볼트와 너트를 다른 줄로</t>
+          <t>리우툴 너트 상품</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M5 × 20mm"</t>
+          <t>옵션 "스텐 육각너트 M5"</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/8531595719</t>
         </is>
       </c>
     </row>
@@ -1956,35 +1956,35 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>M5 육각너트 스텐</t>
+          <t>M5 렌치볼트 스텐 (조정용)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>M5 (맞변 8)</t>
+          <t>M5×8</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>M5×10 · M5×20 마다 1개 (4 + 12)</t>
+          <t>클러치 토크 시험 3 에서 힘이 크면 조절나사를 이것으로</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>리우툴 너트 상품</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>옵션 "스텐 육각너트 M5"</t>
+          <t>옵션 "M5 × 8mm"</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8531595719</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>M5×8</t>
+          <t>M5×12</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>클러치 토크 시험 3 에서 힘이 크면 조절나사를 이것으로</t>
+          <t>클러치 토크 시험 3 에서 힘이 작으면 이것 + 와셔 1장</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M5 × 8mm"</t>
+          <t>옵션 "M5 × 12mm" (와셔 없이 쓰면 금지)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐 (조정용)</t>
+          <t>M5 평와셔 스텐</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>M5×12</t>
+          <t>바깥 12 × 두께 0.5</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>클러치 토크 시험 3 에서 힘이 작으면 이것 + 와셔 1장</t>
+          <t>조정용 M5×12 밑</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M5 × 12mm" (와셔 없이 쓰면 금지)</t>
+          <t>옵션 "1.스텐 평와셔 × M5x12x0.5T"</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
       </c>
     </row>
@@ -2100,35 +2100,35 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>M5 평와셔 스텐</t>
+          <t>M5 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>바깥 12 × 두께 0.5</t>
+          <t>M5×70</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>조정용 M5×12 밑</t>
+          <t>클러치 포크 피벗 1 + 여분 1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>옵션 "1.스텐 평와셔 × M5x12x0.5T"</t>
+          <t>옵션 "M5 × 70mm"</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7440529428</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M5 렌치볼트 스텐</t>
+          <t>M5 나일론 너트 스텐</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>M5×70</t>
+          <t>M5 (DIN985)</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>볼트와 너트를 다른 줄로</t>
+          <t>리우툴 나일론 너트 상품</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>옵션 "M5 × 70mm"</t>
+          <t>옵션 "스텐 나일론 너트 × M5"</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
       </c>
     </row>
@@ -2196,35 +2196,35 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>M5 나일론 너트 스텐</t>
+          <t>M6 렌치볼트 스텐</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>M5 (DIN985)</t>
+          <t>M6×25</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>클러치 포크 피벗 1 + 여분 1</t>
+          <t>모터 받침 4 · 페달 피벗 2 + 여분 1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>리우툴 나일론 너트 상품</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>옵션 "스텐 나일론 너트 × M5"</t>
+          <t>M6×30 이상 금지</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6280971320</t>
+          <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
       </c>
     </row>
@@ -2244,20 +2244,20 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>M6 렌치볼트 스텐</t>
+          <t>M6 육각너트 스텐</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>M6×25</t>
+          <t>M6 (맞변 10)</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>모터 받침 4 · 페달 피벗 2 + 여분 1</t>
+          <t>모터 받침 4 + 여분 1</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>M6×30 이상 금지</t>
+          <t>옵션 "스텐 육각너트 M6"</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6455358137</t>
+          <t>https://www.coupang.com/vp/products/7687671245</t>
         </is>
       </c>
     </row>
@@ -2292,35 +2292,35 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>M6 육각너트 스텐</t>
+          <t>M6 나일론 너트 스텐</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>M6 (맞변 10)</t>
+          <t>M6 (DIN985)</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>모터 받침 4 + 여분 1</t>
+          <t>페달 피벗 2 + 여분 1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>단가 170 → 70 (화면)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>옵션 "스텐 육각너트 M6"</t>
+          <t>옵션 "스텐 나일론 너트 × M6"</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7687671245</t>
+          <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
       </c>
     </row>
@@ -2340,35 +2340,35 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>M6 나일론 너트 스텐</t>
+          <t>목재 나사 스텐 둥근머리</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>M6 (DIN985)</t>
+          <t>4×16, 26개 봉</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>페달 피벗 2 + 여분 1</t>
+          <t>받침 브래킷 8 · 클러치 덮개 4 · 모터 받침 4 · 페달 받침 8 = 24 + 여분</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>단가 170 → 70 (화면)</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>옵션 "스텐 나일론 너트 × M6"</t>
+          <t>옵션 "e)4x16mm-26개", 4×20 이상 안 됨</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2378,22 +2378,22 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6280971320</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7760964029</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="110" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>목재 나사 스텐 둥근머리</t>
+          <t>PLA 필라멘트 LeoPlas 2.85mm 1kg 검정</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>4×16, 26개 봉</t>
+          <t>2.85mm, 1kg</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2401,22 +2401,22 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>받침 브래킷 8 · 클러치 덮개 4 · 모터 받침 4 · 페달 받침 8 = 24 + 여분</t>
+          <t>프레임 0.58 · 핸들 0.70 · 페달 0.44 · 축 부속·새 쿠폰 0.08kg (+15% 포함)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>값 낮춤: 울티메이커 정품 750g 75,900원 × 8 → 일반 2.85mm 1kg × 5. 이미 뽑은 부품(0.17kg + print_next 0.90kg)은 뺌 → 남은 3.66kg + 15% = 4.2kg. 쿠팡엔 국내배송 2.85mm 1kg 이 없어 11번가 (비에스하우스, 무료배송). 새 필라멘트로 00 쿠폰을 다시 뽑아 공차를 정함</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>옵션 "e)4x16mm-26개", 4×20 이상 안 됨</t>
+          <t>PLA 2.85mm 1kg. 옵션 "01 Black" (지름 허용차 화면 미표기)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7760964029</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="95" customHeight="1">
+          <t>https://www.11st.co.kr/products/9216386785</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 2.85mm 1kg 검정</t>
+          <t>PLA 필라멘트 LeoPlas 2.85mm 1kg 주황</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2449,32 +2449,32 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>프레임 0.58 · 핸들 0.70 · 페달 0.44 · 축 부속·새 쿠폰 0.08kg (+15% 포함)</t>
+          <t>기어 1.29kg (+15% = 1.48kg)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 울티메이커 정품 750g 75,900원 × 8 → 일반 2.85mm 1kg × 5. 이미 뽑은 부품(출력 끝 0.17kg, print_next 0.90kg)은 뺌 → 남은 3.63kg + 15% = 4.17kg. 새 필라멘트로 00 쿠폰을 한 번 더 뽑아 공차를 정함</t>
+          <t>같은 상품, 색 옵션만 다름</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>PLA, 지름 2.85mm (허용차 ±0.05 이하 표기), 1kg, 국내배송, 1kg 40,000원 이하. 세 색 같은 브랜드</t>
+          <t>옵션 "05 Orange"</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
+          <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 2.85mm 1kg 주황</t>
+          <t>PLA 필라멘트 LeoPlas 2.85mm 1kg 파랑</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2493,36 +2493,36 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>기어 1.29kg (+15% = 1.48kg)</t>
+          <t>슬리브·변속·클러치 0.81kg (+15% = 0.93kg)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>같은 브랜드, 색만 다름</t>
+          <t>같은 상품, 색 옵션만 다름</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>위와 같음</t>
+          <t>옵션 "06 Blue"</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
+          <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PLA 필라멘트 2.85mm 1kg 파랑</t>
+          <t>2액형 에폭시 접착제</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2.85mm, 1kg</t>
+          <t>주사기형 25ml, 2개 묶음</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2545,32 +2545,32 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>슬리브·변속·클러치 0.78kg (+15% = 0.90kg)</t>
+          <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항 몸통·롤러 핀</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>같은 브랜드, 색만 다름</t>
+          <t>1개씩 2번보다 2개 옵션이 1,250원 쌈</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>위와 같음</t>
+          <t>옵션 "2개"</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=PLA 필라멘트 2.85mm 1kg</t>
+          <t>https://www.coupang.com/vp/products/2725054</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2액형 에폭시 접착제</t>
+          <t>순간접착제</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>주사기형 25ml, 2개 묶음</t>
+          <t>젤 타입 2개</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>레버봉·아이들러 축·클러치 와셔·쿠션 24·가변저항 몸통·롤러 핀</t>
+          <t>덮개 스위치·홀센서·자석</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1개씩 2번보다 2개 옵션이 1,250원 쌈</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/2725054</t>
+          <t>https://www.coupang.com/vp/products/8643897709</t>
         </is>
       </c>
     </row>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>순간접착제</t>
+          <t>자전거 브레이크 케이블 세트</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>젤 타입 2개</t>
+          <t>속선 2 + 아우터 + 끝 캡</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>덮개 스위치·홀센서·자석</t>
+          <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>옵션 "2개"</t>
+          <t>아우터 바깥지름 화면 미표기 (자전거 표준 5) → 받으면 잼</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8643897709</t>
+          <t>https://www.coupang.com/vp/products/8305908512</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>자전거 브레이크 케이블 세트</t>
+          <t>MDF 판</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>속선 2 + 아우터 + 끝 캡</t>
+          <t>12T 300×1200 재단</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
+          <t>바닥판 750×300 + 페달 받침판 450×300</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>아우터 바깥지름 화면 미표기 (자전거 표준 5) → 받으면 잼</t>
+          <t>두께 12, 옵션 "06 MDF"</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8305908512</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/71452005</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="65" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MDF 판</t>
+          <t>투명 아크릴 3T 치수 재단</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>12T 300×1200 재단</t>
+          <t>250×321</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2737,22 +2737,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>바닥판 750×300 + 페달 받침판 450×300</t>
+          <t>덮개 윗판</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>11번가 가격표 방식: 10cm 단위로 올린 30×40cm = 1,000원 × 6. 주문: 옵션 "3T / 투명 / 가공필요없음", 수량 6, 사이즈 칸에 250×321</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>두께 12, 옵션 "06 MDF"</t>
+          <t>두께 3, 투명 (구멍은 직접 Ø3.5)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2762,11 +2762,11 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/71452005</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="65" customHeight="1">
+          <t>https://www.11st.co.kr/products/4918717495</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="35" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -2777,30 +2777,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>250×321</t>
+          <t>200×321</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>덮개 윗판</t>
+          <t>덮개 옆판 2</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11번가 가격표 방식: 10cm 단위로 올린 30×40cm = 1,000원 × 6. 주문: 옵션 "3T / 투명 / 가공필요없음", 수량 6, 사이즈 칸에 250×321</t>
+          <t>같은 방식: 20×40cm = 1,000원 × 5. 주문: 장마다 수량 5, 사이즈 칸에 200×321</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>두께 3, 투명 (구멍은 직접 Ø3.5)</t>
+          <t>같음</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2814,41 +2814,41 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="35" customHeight="1">
+    <row r="50" ht="50" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>투명 아크릴 3T 치수 재단</t>
+          <t>PTFE 그리스 (슈퍼루브)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>200×321</t>
+          <t>85g</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>덮개 옆판 2</t>
+          <t>기어 이·슬리브 키·레일·핸들 캠</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>같은 방식: 20×40cm = 1,000원 × 5. 주문: 장마다 수량 5, 사이즈 칸에 200×321</t>
+          <t>플라스틱에 써도 되는 테프론 그리스. 11번가 5099555102 는 실리콘 그리스라 바꿈</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>같음</t>
+          <t>PTFE(테프론) 합성 그리스</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/4918717495</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/6071008034</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="35" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PTFE 그리스 (슈퍼루브)</t>
+          <t>나사 고정제 록타이트 243</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>85g</t>
+          <t>10ml</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>기어 이·슬리브 키·레일·핸들 캠</t>
+          <t>금속끼리 나사: 칼라·핸들 무두볼트, 모터 M6 (마봉이 가늘면 끝판 베어링 자리)</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>플라스틱에 써도 되는 테프론 그리스. 11번가 5099555102 는 실리콘 그리스라 바꿈</t>
+          <t>그대로 (단가 7,790 → 8,580)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>PTFE(테프론) 합성 그리스</t>
+          <t>243 (중강도, 분해 가능)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6071008034</t>
+          <t>https://www.11st.co.kr/products/7426834008</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>나사 고정제 록타이트 243</t>
+          <t>열수축 튜브 세트</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>10ml</t>
+          <t>1~14mm 164개</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>금속끼리 나사: 칼라·핸들 무두볼트, 모터 M6 (마봉이 가늘면 끝판 베어링 자리)</t>
+          <t>홀센서·가변저항·스위치 납땜부 절연</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>그대로 (단가 7,790 → 8,580)</t>
+          <t>전자부품을 동신전자 한 곳으로 묶음</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>243 (중강도, 분해 가능)</t>
+          <t>옵션 "(PP-K022) 열수축튜브 세트"</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>11번가 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://www.11st.co.kr/products/7426834008</t>
+          <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>열수축 튜브 세트</t>
+          <t>케이블 타이</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>1~14mm 164개</t>
+          <t>100개, 흑색</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>홀센서·가변저항·스위치 납땜부 절연</t>
+          <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>전자부품을 동신전자 한 곳으로 묶음</t>
+          <t>로켓배송 (11번가는 배송비 3,000)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>옵션 "(PP-K022) 열수축튜브 세트"</t>
+          <t>옵션 "100개, 흑색"</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828751</t>
+          <t>https://www.coupang.com/vp/products/8850608631</t>
         </is>
       </c>
     </row>
@@ -3012,35 +3012,35 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>케이블 타이</t>
+          <t>신호선 0.3SQ (약 22AWG) 10색</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>100개, 흑색</t>
+          <t>10색 × 1m 세트</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>배선 정리 (돌아가는 부품에 안 닿게)</t>
+          <t>페달·핸들 가변저항, 홀센서 → 아두이노 (5세트 = 색마다 5m)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>로켓배송 (11번가는 배송비 3,000)</t>
+          <t>동신전자로 묶음</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>옵션 "100개, 흑색"</t>
+          <t>옵션 "선택 01) 10색선 0.3SQ 1M"</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8850608631</t>
+          <t>https://www.coupang.com/vp/products/9183828539</t>
         </is>
       </c>
     </row>
@@ -3060,35 +3060,35 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>신호선 0.3SQ (약 22AWG) 10색</t>
+          <t>탁상 바이스 ITL 80mm</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>10색 × 1m 세트</t>
+          <t>주물, 360도 회전, 책상 모서리 클램프 (ITL-0124)</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>페달·핸들 가변저항, 홀센서 → 아두이노 (5세트 = 색마다 5m)</t>
+          <t>D컷 작업 때 축 고정 (조에 알루미늄판이나 두꺼운 종이를 댐)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>동신전자로 묶음</t>
+          <t>값 낮춤: ITL 100mm 34,900원 → 같은 회사 80mm (케이씨제이, 무료배송)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>옵션 "선택 01) 10색선 0.3SQ 1M"</t>
+          <t>주물, 조 폭 80mm, 클램프 고정. 옵션 "(단일 상품)"</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3098,22 +3098,22 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828539</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="65" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9035202709</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="35" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>디지털 캘리퍼스</t>
+          <t>철공용 평줄 중목</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>150mm, 분해능 0.01mm</t>
+          <t>250mm</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>쿠폰 공차 · D컷 두 면 사이 10.00 · 마봉·가변저항·스프링·호스 실측</t>
+          <t>D컷 마무리 (그라인더 다음)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 미쓰도요 156,400원 → 일반 디지털. 비교 측정(D컷 25mm 마다, 쿠폰)은 같은 캘리퍼스로 하므로 정확도 ±0.03 이면 충분</t>
+          <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>분해능 0.01mm, 150mm, 스텐 몸체, 국내배송, 30,000원 이하</t>
+          <t>철공용, 평줄, 중목</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=디지털 캘리퍼스 150mm</t>
+          <t>https://www.coupang.com/vp/products/8997744652</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>탁상 바이스</t>
+          <t>철공용 평줄 세목</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>조 폭 75~100mm, 책상에 클램프 고정</t>
+          <t>200mm</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
@@ -3169,32 +3169,32 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>D컷 작업 때 축 고정 (조에 알루미늄판이나 두꺼운 종이를 댐)</t>
+          <t>D컷 마지막 0.05mm</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: ITL 34,900원 → 같은 크기 더 싼 것</t>
+          <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>주물, 조 폭 75mm 이상, 클램프로 책상 고정, 국내배송, 25,000원 이하</t>
+          <t>철공용, 평줄, 세목</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=탁상 바이스</t>
+          <t>https://www.coupang.com/vp/products/8997744821</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>철공용 평줄 중목</t>
+          <t>플랩 디스크 100mm #80</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>250mm</t>
+          <t>10개 봉</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
@@ -3217,22 +3217,22 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>D컷 마무리 (그라인더 다음)</t>
+          <t>D컷 거친 깎기 (3장 필요)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>이엑스파워 (로켓배송)</t>
+          <t>디어포스 (로켓배송)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>철공용, 평줄, 중목</t>
+          <t>지름 100, #80, 구멍 16 (화면 미표기, 4인치 그라인더 가정)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744652</t>
+          <t>https://www.coupang.com/vp/products/9416862249</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>철공용 평줄 세목</t>
+          <t>절단석 105mm 두께 1mm</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>200mm</t>
+          <t>5개 봉</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -3265,22 +3265,22 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>D컷 마지막 0.05mm</t>
+          <t>마봉 Ø12 · 스텐 Ø6 자르기 (9번 자름)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>이엑스파워 (로켓배송)</t>
+          <t>켈코 (4인치 그라인더용)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>철공용, 평줄, 세목</t>
+          <t>지름 105, 두께 1, 철재용, 구멍 16 (화면 미표기)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8997744821</t>
+          <t>https://www.coupang.com/vp/products/9375758010</t>
         </is>
       </c>
     </row>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>플랩 디스크 100mm #80</t>
+          <t>보안경 (측면 보호)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10개 봉</t>
+          <t>투명</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -3313,22 +3313,22 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>D컷 거친 깎기 (3장 필요)</t>
+          <t>그라인더 작업 (불티, 작업하는 1명)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>디어포스 (로켓배송)</t>
+          <t>명신광학 J-67A 국산</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>지름 100, #80, 구멍 16 (화면 미표기, 4인치 그라인더 가정)</t>
+          <t>옵션 "FREE × 투명"</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9416862249</t>
+          <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>절단석 105mm 두께 1mm</t>
+          <t>NBR 코팅 장갑 가드맨</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>5개 봉</t>
+          <t>L, 3켤레</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3361,22 +3361,22 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>마봉 Ø12 · 스텐 Ø6 자르기 (9번 자름)</t>
+          <t>그라인더·줄 작업</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>켈코 (4인치 그라인더용)</t>
+          <t>값 낮춤: 절단 방지 장갑 2개 11,300원 → 일반 코팅 장갑 (로켓배송)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>지름 105, 두께 1, 철재용, 구멍 16 (화면 미표기)</t>
+          <t>옵션 "회색 × L × 3개"</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9375758010</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/8531708909</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="50" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>보안경 (측면 보호)</t>
+          <t>코발트 드릴 날 2.5mm</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>투명</t>
+          <t>육각 생크, 3개</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3409,22 +3409,22 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>그라인더 작업 (불티, 작업하는 1명)</t>
+          <t>MDF 목재나사 밑구멍 Ø2.5 (아크릴 Ø3.4 는 보유)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>명신광학 J-67A 국산</t>
+          <t>값 낮춤: 19개 세트 7,740원 + 배송비 → 2.5mm 만 (종원 HSS-Co, 로켓배송). 3,000 이하 로켓 상품 없음</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>옵션 "FREE × 투명"</t>
+          <t>지름 2.5mm. 옵션 "3개"</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3434,22 +3434,22 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8800840444</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/1479107481</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>NBR 코팅 장갑</t>
+          <t>C클램프 4인치</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>최대 벌림 105mm, 2개 묶음</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3457,32 +3457,32 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>그라인더·줄 작업</t>
+          <t>핸들 받침을 책상 모서리에 고정</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 절단 방지 장갑 2개 11,300원 → 일반 코팅 장갑</t>
+          <t>엠케이</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>NBR 코팅, L, 국내배송 (로켓배송이면 좋음), 5,000원 이하</t>
+          <t>벌림 105 (받침판 8 + 책상 두께), 목 깊이 화면 미표기 (받침판 앞 끝에서 25mm 안을 물리므로 35 이상이면 됨)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=NBR 코팅장갑</t>
+          <t>https://www.coupang.com/vp/products/8261073812</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>HSS 드릴 날 2.5mm</t>
+          <t>아두이노 레오나르도 R3 + USB 케이블</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>ATmega32u4</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -3505,70 +3505,70 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MDF 목재나사 밑구멍 Ø2.5 (아크릴 Ø3.4 는 보유)</t>
+          <t>게임 입력·모터 허가</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 19개 세트 7,740원 + 배송비 → 필요한 2.5mm 하나</t>
+          <t>값 낮춤: 여분 뺌</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>HSS, 지름 2.5mm, 국내배송 (로켓배송이면 좋음), 3,000원 이하</t>
+          <t>레오나르도(32u4) — 우노 안 됨</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>찾기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/np/search?q=HSS 드릴날 2.5mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="50" customHeight="1">
+          <t>https://www.coupang.com/vp/products/1119152790</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="35" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C클램프 4인치</t>
+          <t>홀센서 A3144</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>최대 벌림 105mm, 2개 묶음</t>
+          <t>3핀</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>핸들 받침을 책상 모서리에 고정</t>
+          <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>엠케이</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>벌림 105 (받침판 8 + 책상 두께), 목 깊이 화면 미표기 (받침판 앞 끝에서 25mm 안을 물리므로 35 이상이면 됨)</t>
+          <t>A3144 (래치 아님)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8261073812</t>
+          <t>https://www.coupang.com/vp/products/8520223332</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>아두이노 레오나르도 R3 + USB 케이블</t>
+          <t>네오디뮴 자석</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ATmega32u4</t>
+          <t>Ø6×3, 40개</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -3601,22 +3601,22 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>게임 입력·모터 허가</t>
+          <t>러그 3 · 표시 바퀴 4 + 여분</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 여분 뺌</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>레오나르도(32u4) — 우노 안 됨</t>
+          <t>지름 6 두께 3, 옵션 "40개입"</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3626,45 +3626,45 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/1119152790</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/7119515778</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="65" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>홀센서 A3144</t>
+          <t>가변저항 10K WH148 톱니 축</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>3핀</t>
+          <t>16mm, 축 15mm, 부싱 M7, 3핀</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
+          <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>D(반달)축 국내품이 없어 톱니 축 → 페달 팔(80)·핸들 캠(93)의 축 구멍을 압입 구멍(POT_HOLE)으로 바꿈. B(직선형)·가운데 딸깍은 화면 미표기 → 받으면 확인</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>A3144 (래치 아님)</t>
+          <t>10K, 16mm, 축 15mm, 부싱 M7. 옵션 "가변저항 10K"</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8520223332</t>
+          <t>https://www.coupang.com/vp/products/8718871111</t>
         </is>
       </c>
     </row>
@@ -3684,20 +3684,20 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>네오디뮴 자석</t>
+          <t>마이크로스위치 KW-11-3Z</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Ø6×3, 40개</t>
+          <t>레버형</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>러그 3 · 표시 바퀴 4 + 여분</t>
+          <t>덮개 열림 감지 1 + 여분 1</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3705,14 +3705,10 @@
           <t>그대로</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>지름 6 두께 3, 옵션 "40개입"</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3722,45 +3718,45 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/7119515778</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="65" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9167678186</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="35" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>가변저항 10K WH148 톱니 축</t>
+          <t>점퍼 케이블 F-M</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>16mm, 축 15mm, 부싱 M7, 3핀</t>
+          <t>40P 40cm</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
+          <t>센서 배선</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>D(반달)축 국내품이 없어 톱니 축 → 페달 팔(80)·핸들 캠(93)의 축 구멍을 압입 구멍(POT_HOLE)으로 바꿈. B(직선형)·가운데 딸깍은 화면 미표기 → 받으면 확인</t>
+          <t>동신전자로 묶음 (5,300 → 1,300)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>10K, 16mm, 축 15mm, 부싱 M7. 옵션 "가변저항 10K"</t>
+          <t>옵션 "(PP-A848) 점퍼케이블 40핀 40cm 암/수"</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3770,7 +3766,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/8718871111</t>
+          <t>https://www.coupang.com/vp/products/9183828363</t>
         </is>
       </c>
     </row>
@@ -3780,31 +3776,35 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>마이크로스위치 KW-11-3Z</t>
+          <t>만능기판 양면 2.54</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>레버형</t>
+          <t>28×43홀 (약 71×109mm)</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>덮개 열림 감지 1 + 여분 1</t>
+          <t>센서 배선 기판</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>20장 묶음이 16,900 으로 올라 필요한 장수만</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>옵션 "(PP-D021) 에폭시 양면기판 28x43"</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9167678186</t>
+          <t>https://www.coupang.com/vp/products/9181560693</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>점퍼 케이블 F-M</t>
+          <t>자동차 릴레이 12V 40A + 소켓</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>40P 40cm</t>
+          <t>4핀, 배선된 소켓</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -3837,22 +3837,22 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>센서 배선</t>
+          <t>모터 주 스위치</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>동신전자로 묶음 (5,300 → 1,300)</t>
+          <t>값 낮춤: 여분 뺌</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>옵션 "(PP-A848) 점퍼케이블 40핀 40cm 암/수"</t>
+          <t>코일 12V, 접점 30A 이상</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9183828363</t>
+          <t>https://www.coupang.com/vp/products/6667848502</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>만능기판 양면 2.54</t>
+          <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>28×43홀 (약 71×109mm)</t>
+          <t>15A 포함, 홀더 4 + 퓨즈 12</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>센서 배선 기판</t>
+          <t>배터리 + 단자 바로 옆</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>20장 묶음이 16,900 으로 올라 필요한 장수만</t>
+          <t>그대로 (여분 퓨즈 포함)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>옵션 "(PP-D021) 에폭시 양면기판 28x43"</t>
+          <t>15A 퓨즈 포함</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9181560693</t>
+          <t>https://www.coupang.com/vp/products/9663070188</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3920,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>자동차 릴레이 12V 40A + 소켓</t>
+          <t>비상정지 스위치 22mm + 1구 박스</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>4핀, 배선된 소켓</t>
+          <t>LAS0-K-11TSA, 1a1b</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -3933,22 +3933,22 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>모터 주 스위치</t>
+          <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 여분 뺌</t>
+          <t>G마켓 스위치 + 11번가 박스 대신 한 세트 (동신전자)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>코일 12V, 접점 30A 이상</t>
+          <t>b접점 있음 (1·2번 NC), 장착 Ø22.5, 박스 BXA-22/1/Y 포함. KC 미인증 표기</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/6667848502</t>
+          <t>https://www.coupang.com/vp/products/9169916764</t>
         </is>
       </c>
     </row>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>블레이드 퓨즈 + 인라인 홀더 세트</t>
+          <t>5V 릴레이 모듈 1채널 KY-019</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>15A 포함, 홀더 4 + 퓨즈 12</t>
+          <t>1채널</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3981,22 +3981,22 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>배터리 + 단자 바로 옆</t>
+          <t>아두이노 감시 → 주 릴레이 코일 차단</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>그대로 (여분 퓨즈 포함)</t>
+          <t>동신전자로 묶음</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>15A 퓨즈 포함</t>
+          <t>5V, 1채널 (트리거 방식은 펌웨어로 맞춤)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9663070188</t>
+          <t>https://www.coupang.com/vp/products/9162331915</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4016,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>비상정지 스위치 22mm + 1구 박스</t>
+          <t>다이오드 1N4007</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>LAS0-K-11TSA, 1a1b</t>
+          <t>10개</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -4029,22 +4029,22 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
+          <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>G마켓 스위치 + 11번가 박스 대신 한 세트 (동신전자)</t>
+          <t>하진전자로 묶음</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>b접점 있음 (1·2번 NC), 장착 Ø22.5, 박스 BXA-22/1/Y 포함. KC 미인증 표기</t>
+          <t>1N4007</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9169916764</t>
+          <t>https://www.coupang.com/vp/products/9705767581</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4064,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>5V 릴레이 모듈 1채널 KY-019</t>
+          <t>저항 1/4W 10kΩ</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>1채널</t>
+          <t>10개</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -4077,22 +4077,22 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>아두이노 감시 → 주 릴레이 코일 차단</t>
+          <t>안전 회로 감지 분압 (12V → 아두이노 A4)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>동신전자로 묶음</t>
+          <t>30종 세트 대신 필요한 값만</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>5V, 1채널 (트리거 방식은 펌웨어로 맞춤)</t>
+          <t>옵션 "10K"</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9162331915</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>다이오드 1N4007</t>
+          <t>저항 1/4W 4.7kΩ</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4125,22 +4125,22 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
+          <t>안전 회로 감지 분압</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>하진전자로 묶음</t>
+          <t>같은 상품의 다른 옵션</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1N4007</t>
+          <t>옵션 "4.7K"</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9705767581</t>
+          <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
       </c>
     </row>
@@ -4160,35 +4160,35 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>저항 1/4W 10kΩ</t>
+          <t>실리콘 전선 16AWG 빨강·검정</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
+          <t>1m 세트</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>안전 회로 감지 분압 (12V → 아두이노 A4)</t>
+          <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>30종 세트 대신 필요한 값만</t>
+          <t>그대로</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>옵션 "10K"</t>
+          <t>16AWG 이상</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
+          <t>https://www.coupang.com/vp/products/7225302003</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>저항 1/4W 4.7kΩ</t>
+          <t>절연 암 평형 단자 250 (6.3mm)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>10개</t>
+          <t>10개 봉</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
@@ -4221,22 +4221,22 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>안전 회로 감지 분압</t>
+          <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>같은 상품의 다른 옵션</t>
+          <t>동신전자로 묶음 (전과 같은 10개)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>옵션 "4.7K"</t>
+          <t>6.3mm 암, 절연형 (전선 굵기 범위 화면 미표기)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4246,45 +4246,37 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9701925630</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="35" customHeight="1">
+          <t>https://www.coupang.com/vp/products/9181548711</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="65" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>실리콘 전선 16AWG 빨강·검정</t>
+          <t>배송비</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>1m 세트</t>
+          <t>판매처별 합계</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>그대로</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>16AWG 이상</t>
-        </is>
-      </c>
+          <t>판매처 17곳: 3,000 × 10 · 3,500 × 2 · 4,000 · 2,800 × 2 · 2,700 · 2,500 (2026-10-23 화면). 로켓배송 12개와 무료배송 9곳은 0. 제주·도서산간 추가 제외</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>쿠팡 화면 2026-10-22</t>
+          <t>쿠팡 화면 2026-10-23</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4292,101 +4284,13 @@
           <t>확인</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/7225302003</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="35" customHeight="1">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>절연 암 평형 단자 250 (6.3mm)</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>10개 봉</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>동신전자로 묶음 (전과 같은 10개)</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>6.3mm 암, 절연형 (전선 굵기 범위 화면 미표기)</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-22</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.coupang.com/vp/products/9181548711</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="95" customHeight="1">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>배송비</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>판매처별 합계</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>판매처 18곳 54,800 (2026-10-22 화면 합계) − 소망트레이딩(베어링)·공구랜드(드릴) + 베어링 판매처 2곳·G마켓 칼라 3,000씩 (추정). 새로 고르는 줄은 로켓배송(19,800 이상 무료)이나 이미 있는 판매자로 고르면 늘지 않음</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>찾기</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>예상단가: 쿠팡·11번가 화면 2026-10-22 (다른 세션에서 확인). 상태 "검색"은 화면 확인 필요, "찾기"는 값을 낮추려고 새로 고를 줄 (단가는 추정, 상한 가격은 "꼭 맞아야 할 것" 칸). 모두 국내배송. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더(4인치 가정)는 보유.</t>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>예상단가: 쿠팡·11번가 화면 2026-10-23 (다른 세션에서 확인). 모두 국내배송. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더(4인치 가정)는 보유. 캘리퍼스는 사지 않음 (사용자 결정 2026-10-23). 레일 칼라는 국내배송 상품이 없어 출력 (50c).</t>
         </is>
       </c>
     </row>

--- a/v4/물품계획서_근거.xlsx
+++ b/v4/물품계획서_근거.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -451,14 +451,18 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>no</t>
@@ -486,25 +490,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>필요 (설계에서 셈)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>사는 양</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>남음</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>고른 이유·바뀐 점</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>꼭 맞아야 할 것</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>가격 근거</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>링크</t>
         </is>
@@ -532,27 +556,41 @@
           <t>변속기 19 (끝판 4 · 출력 기어 12 · 아이들러 2 · 클러치 파일럿 1) + 핸들 3 (축 2 · 롤러 1) + 여분 8</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>값 낮춤: NSK 낱개 3,000원 × 25 → 일반 10개 묶음 (디오상공사, 무료배송). 압입 구멍은 00 쿠폰으로 이 베어링에 맞춤</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>6001ZZ, 12×28×8, 철판 실드. 옵션 "6001ZZ - 가성비 × 10개"</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8630678241</t>
         </is>
@@ -580,27 +618,41 @@
           <t>클러치 릴리스 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>값 낮춤: NSK 4,000원 → KYK (나라기업). 6001 판매자의 10개 묶음(7,000)보다 2개 + 배송비가 1,800원 쌈</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>6003ZZ, 17×35×10. 옵션 "수량: 1개"</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8230435105</t>
         </is>
@@ -628,27 +680,41 @@
           <t>봉 1: 입력축 435 · 출력축 358 · 레버봉 160 / 봉 2: 핸들 축 106 · 롤러 핀 22 · 아이들러 축 55 / 봉 3~6: D컷 실수 대비 (모두 절단석으로 직접 자름)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>G마켓 소망트레이딩 연마봉이 지워졌고, 쿠팡·11번가의 Ø12 연마봉은 모두 열처리품이라 줄로 D컷을 못 함 → 열처리 안 된 SM45C 마봉. 연마(h7)가 아니므로 받으면 지름을 잼 (11.95 보다 가늘면 끝판 베어링 자리에 록타이트 243)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>SM45C, Ø12, 1m × 6, 열처리 안 됨. 옵션 "SM45C /직경12mm/1m6개 × 1세트"</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9472297916</t>
         </is>
@@ -676,27 +742,41 @@
           <t>변속 레일 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>G마켓 상품을 열 수 없어 쿠팡 국내 상품으로. 절단 옵션이 없어 절단석으로 자르고 끝을 줄로 모따기</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>스텐, 지름 6, 1m. 옵션 "국내최초 스텐환봉 절단판매 1M (6파이)"</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7575963441</t>
         </is>
@@ -724,27 +804,41 @@
           <t>도그 24 + 여분</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>옵션 "M5 (+)공차 / 25mm × 100개"</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9743421687</t>
         </is>
@@ -772,27 +866,41 @@
           <t>스프로킷 커플링 6 + 여분 2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>옵션 "(+) 0~+0.01 × 5x40"</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8532354386</t>
         </is>
@@ -822,25 +930,41 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>144mm (6mm × 24)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>약 2m</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>그대로. 재질 표기 없음(진공호스) → 받으면 바깥지름을 재서 CUSH_OD</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>안 5 × 바깥 10</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8558801755</t>
         </is>
@@ -868,27 +992,41 @@
           <t>클러치 원판 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>옵션 "M16 × 50mm"</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6305734042</t>
         </is>
@@ -918,25 +1056,41 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>링 2개 (바깥 Ø50)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>A4 2장</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>옵션 "콜크쉬트:연갈색 2mm×A4×2매"</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/4845669553</t>
         </is>
@@ -964,27 +1118,41 @@
           <t>러그 디텐트 3</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>지름 6, 옵션 "50개"</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9638493021</t>
         </is>
@@ -1012,27 +1180,41 @@
           <t>변속기 9 (포크 카트리지 3 · 클러치 3 · 레버 후진 잠금 1 · 페달 복귀 2) + 핸들 복귀 2 + 여분 4</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>판매 중인 기성품 (사용자 결정). 사진으로 센 권수 5.5 → k ≈ 2.8 N/mm, 밀착 8.3. 자유장이 C252(32)보다 짧아 카트리지·클러치 컵·레버 스페이서·페달·핸들 길이를 이 값으로 다시 계산함. 받으면 물 무게로 k 실측 (설계서 10장)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>SUS304, 선경 1.5, 외경 18, 자유장 25 (스프링팜). 옵션 "수량: 1개"</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/4387963066</t>
         </is>
@@ -1060,27 +1242,41 @@
           <t>러그 디텐트 3 + 여분 3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>판매 중인 기성품. 권수 약 6 → k 0.57 N/mm, 5mm 눌러 2.85N (C147 과 같은 범위), 밀착 2.4</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>선경 0.4, 외경 5, 자유장 10. 옵션 "스프링 0.4X5X10"</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8501265889</t>
         </is>
@@ -1108,27 +1304,41 @@
           <t>포크 카트리지 뚜껑 6 · 디텐트 3 + 여분 2</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>옵션 "M3 × 8mm"</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1156,27 +1366,41 @@
           <t>클러치 포크 속선 누름 1 · 출력 레일 칼라 조임 6 + 여분 3</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>레일 칼라를 출력으로 바꿔 6개 추가 (국내배송 칼라 판매 종료)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>옵션 "M3 × 10mm"</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1204,27 +1428,41 @@
           <t>칼라 7 · 클러치 덮개 7 · 축 끝 덮개 4 · 바퀴 덮개 2 · 아크릴 14 · 핸들 뒤 덮개 4 = 38 + 여분 6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>옵션 "M3 × 12mm"</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1252,27 +1490,41 @@
           <t>바퀴 덮개 받침 2 + 여분 1</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>옵션 "M3 × 16mm"</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1300,27 +1552,41 @@
           <t>슬리브 결합 9 + 여분 2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로 (너트는 상품 번호가 다름)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>옵션 "M3 × 20mm"</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1348,27 +1614,41 @@
           <t>러그 6 + 여분 2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>M3×30 안 됨 (머리가 캐리어에 닿음)</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1396,27 +1676,41 @@
           <t>끝 채움판 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>옵션 "M3 × 50mm"</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1444,27 +1738,41 @@
           <t>슬리브 결합 9 · 핸들 무두볼트 2 + 여분 4</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>리우툴 너트 상품</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>맞변 5.5. 옵션 "스텐 육각너트 M3"</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8532240860</t>
         </is>
@@ -1492,27 +1800,41 @@
           <t>표시 바퀴 1 · 핸들 허브 1 · 캠 1 + 여분 2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>핸들 받침 v4.2 는 2개</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>오목끝(컵), 길이 8. 옵션 "M3 × 8mm"</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7974822838</t>
         </is>
@@ -1540,27 +1862,41 @@
           <t>아크릴 나사 밑 14 · 속선 누름 1 + 여분 5</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>옵션 "1.스텐 평와셔 × M3x8x0.5T"</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
@@ -1588,27 +1924,41 @@
           <t>클러치 포크 브래킷 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>옵션 "M4 × 16mm"</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1636,27 +1986,41 @@
           <t>페달 발판 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>옵션 "M4 × 25mm"</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1684,27 +2048,41 @@
           <t>케이지 4 · 피벗 8 · 게이트 4 · 받침 브래킷 4 · 핸들 몸체 4 = 24 + 여분 3</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>옵션 "M4 × 30mm"</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1732,27 +2110,41 @@
           <t>클러치 기둥 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>옵션 "M4 × 60mm"</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1780,27 +2172,41 @@
           <t>M4 볼트마다 1개 (16: 5 · 25: 5 · 30: 27 · 60: 4)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>리우툴 너트 상품</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>옵션 "스텐 육각너트 M4"</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8531939792</t>
         </is>
@@ -1828,27 +2234,41 @@
           <t>클러치 조절나사 3 + 여분 1</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>M5×12 이상 금지 (클러치 토크 초과)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1876,27 +2296,41 @@
           <t>클러치 릴리스 누름 3 · 핸들 고정 6 (PCD 70 6구멍 가정) + 여분 3</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>옵션 "M5 × 20mm"</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -1924,27 +2358,41 @@
           <t>M5×10 · M5×20 마다 1개 (4 + 12)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>리우툴 너트 상품</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>옵션 "스텐 육각너트 M5"</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8531595719</t>
         </is>
@@ -1972,27 +2420,41 @@
           <t>클러치 토크 시험 3 에서 힘이 크면 조절나사를 이것으로</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>옵션 "M5 × 8mm"</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -2020,27 +2482,41 @@
           <t>클러치 토크 시험 3 에서 힘이 작으면 이것 + 와셔 1장</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>옵션 "M5 × 12mm" (와셔 없이 쓰면 금지)</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -2068,27 +2544,41 @@
           <t>조정용 M5×12 밑</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>옵션 "1.스텐 평와셔 × M5x12x0.5T"</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7440529428</t>
         </is>
@@ -2116,27 +2606,41 @@
           <t>클러치 포크 피벗 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>볼트와 너트를 다른 줄로</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>옵션 "M5 × 70mm"</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -2164,27 +2668,41 @@
           <t>클러치 포크 피벗 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>리우툴 나일론 너트 상품</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>옵션 "스텐 나일론 너트 × M5"</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
@@ -2212,27 +2730,41 @@
           <t>모터 받침 4 · 페달 피벗 2 + 여분 1</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>M6×30 이상 금지</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6455358137</t>
         </is>
@@ -2260,27 +2792,41 @@
           <t>모터 받침 4 + 여분 1</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>옵션 "스텐 육각너트 M6"</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7687671245</t>
         </is>
@@ -2308,27 +2854,41 @@
           <t>페달 피벗 2 + 여분 1</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>단가 170 → 70 (화면)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>옵션 "스텐 나일론 너트 × M6"</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6280971320</t>
         </is>
@@ -2356,33 +2916,47 @@
           <t>받침 브래킷 8 · 클러치 덮개 4 · 모터 받침 4 · 페달 받침 8 = 24 + 여분</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>옵션 "e)4x16mm-26개", 4×20 이상 안 됨</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7760964029</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="110" customHeight="1">
+    <row r="41" ht="140" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -2401,30 +2975,46 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>프레임 0.58 · 핸들 0.70 · 페달 0.44 · 축 부속·새 쿠폰 0.08kg (+15% 포함)</t>
+          <t>프레임·덮개 0.57 · 핸들 0.68 · 페달 0.40kg (+15% = 1.89kg)</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>값 낮춤: 울티메이커 정품 750g 75,900원 × 8 → 일반 2.85mm 1kg × 5. 이미 뽑은 부품(0.17kg + print_next 0.90kg)은 뺌 → 남은 3.66kg + 15% = 4.2kg. 쿠팡엔 국내배송 2.85mm 1kg 이 없어 11번가 (비에스하우스, 무료배송). 새 필라멘트로 00 쿠폰을 다시 뽑아 공차를 정함</t>
+          <t>1.89kg (권장 Cura 설정, 여유 15% 포함)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>값 낮춤: 울티메이커 정품 750g 75,900원 × 8 → 일반 2.85mm 1kg × 5. 이미 뽑은 부품(0.17kg + print_next 0.90kg)은 뺌. 사용자 Cura 권장 설정(층 0.2, 벽 1.6, 채움 40%, 큰 판·덮개 20%)으로 남은 4.14kg + 15% = 4.76kg (설계서 6장). 쿠팡엔 국내배송 2.85mm 1kg 이 없어 11번가 (비에스하우스, 무료배송). 새 필라멘트로 00 쿠폰을 다시 뽑아 공차를 정함</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
           <t>PLA 2.85mm 1kg. 옵션 "01 Black" (지름 허용차 화면 미표기)</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
@@ -2449,30 +3039,46 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>기어 1.29kg (+15% = 1.48kg)</t>
+          <t>기어 1.57 · 축 부속·새 쿠폰 0.07kg (+15% = 1.89kg)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
+          <t>1.89kg</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2kg</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>같은 상품, 색 옵션만 다름</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>옵션 "05 Orange"</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
@@ -2497,30 +3103,46 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>슬리브·변속·클러치 0.81kg (+15% = 0.93kg)</t>
+          <t>슬리브·변속·클러치 0.85kg (+15% = 0.98kg)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>0.98kg</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>같은 상품, 색 옵션만 다름</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>옵션 "06 Blue"</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>https://www.11st.co.kr/products/9216386785</t>
         </is>
@@ -2550,25 +3172,41 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>1개씩 2번보다 2개 옵션이 1,250원 쌈</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>옵션 "2개"</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/2725054</t>
         </is>
@@ -2598,25 +3236,41 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>옵션 "2개"</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8643897709</t>
         </is>
@@ -2644,33 +3298,47 @@
           <t>클러치 페달 → 클러치 포크 (속선 1 여분)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>아우터 바깥지름 화면 미표기 (자전거 표준 5) → 받으면 잼</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8305908512</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="35" customHeight="1">
+    <row r="47" ht="65" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -2694,25 +3362,41 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>변속기 725×270 + 페달 받침 2개 (각 140×120)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>750×300 + 450×300</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>두께 12, 옵션 "06 MDF"</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/71452005</t>
         </is>
@@ -2740,27 +3424,41 @@
           <t>덮개 윗판</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>11번가 가격표 방식: 10cm 단위로 올린 30×40cm = 1,000원 × 6. 주문: 옵션 "3T / 투명 / 가공필요없음", 수량 6, 사이즈 칸에 250×321</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>두께 3, 투명 (구멍은 직접 Ø3.5)</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>https://www.11st.co.kr/products/4918717495</t>
         </is>
@@ -2788,27 +3486,41 @@
           <t>덮개 옆판 2</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>같은 방식: 20×40cm = 1,000원 × 5. 주문: 장마다 수량 5, 사이즈 칸에 200×321</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>같음</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>https://www.11st.co.kr/products/4918717495</t>
         </is>
@@ -2838,25 +3550,41 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>플라스틱에 써도 되는 테프론 그리스. 11번가 5099555102 는 실리콘 그리스라 바꿈</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>PTFE(테프론) 합성 그리스</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6071008034</t>
         </is>
@@ -2886,25 +3614,41 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>그대로 (단가 7,790 → 8,580)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>243 (중강도, 분해 가능)</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>11번가 화면 2026-10-23</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>https://www.11st.co.kr/products/7426834008</t>
         </is>
@@ -2934,25 +3678,41 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>전자부품을 동신전자 한 곳으로 묶음</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>옵션 "(PP-K022) 열수축튜브 세트"</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9183828751</t>
         </is>
@@ -2982,25 +3742,41 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>로켓배송 (11번가는 배송비 3,000)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>옵션 "100개, 흑색"</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8850608631</t>
         </is>
@@ -3030,25 +3806,41 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t>약 40m (페달까지 2m 가정)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>50m (색마다 5m)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>동신전자로 묶음</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>옵션 "선택 01) 10색선 0.3SQ 1M"</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9183828539</t>
         </is>
@@ -3078,25 +3870,41 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>값 낮춤: ITL 100mm 34,900원 → 같은 회사 80mm (케이씨제이, 무료배송)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>주물, 조 폭 80mm, 클램프 고정. 옵션 "(단일 상품)"</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9035202709</t>
         </is>
@@ -3126,25 +3934,41 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>철공용, 평줄, 중목</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8997744652</t>
         </is>
@@ -3174,25 +3998,41 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>이엑스파워 (로켓배송)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>철공용, 평줄, 세목</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8997744821</t>
         </is>
@@ -3220,27 +4060,41 @@
           <t>D컷 거친 깎기 (3장 필요)</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>디어포스 (로켓배송)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>지름 100, #80, 구멍 16 (화면 미표기, 4인치 그라인더 가정)</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9416862249</t>
         </is>
@@ -3270,25 +4124,41 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
+          <t>자르기 9번 (Ø12 5 · Ø6 4)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>5장</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>켈코 (4인치 그라인더용)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>지름 105, 두께 1, 철재용, 구멍 16 (화면 미표기)</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9375758010</t>
         </is>
@@ -3318,25 +4188,41 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>명신광학 J-67A 국산</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>옵션 "FREE × 투명"</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8800840444</t>
         </is>
@@ -3366,25 +4252,41 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>값 낮춤: 절단 방지 장갑 2개 11,300원 → 일반 코팅 장갑 (로켓배송)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>옵션 "회색 × L × 3개"</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8531708909</t>
         </is>
@@ -3414,25 +4316,41 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>값 낮춤: 19개 세트 7,740원 + 배송비 → 2.5mm 만 (종원 HSS-Co, 로켓배송). 3,000 이하 로켓 상품 없음</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>지름 2.5mm. 옵션 "3개"</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/1479107481</t>
         </is>
@@ -3460,27 +4378,41 @@
           <t>핸들 받침을 책상 모서리에 고정</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>엠케이</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>벌림 105 (받침판 8 + 책상 두께), 목 깊이 화면 미표기 (받침판 앞 끝에서 25mm 안을 물리므로 35 이상이면 됨)</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8261073812</t>
         </is>
@@ -3508,27 +4440,41 @@
           <t>게임 입력·모터 허가</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>값 낮춤: 여분 뺌</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>레오나르도(32u4) — 우노 안 됨</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/1119152790</t>
         </is>
@@ -3556,27 +4502,41 @@
           <t>기어 위치 6 · 출력 rpm 1 + 여분 3</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>A3144 (래치 아님)</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8520223332</t>
         </is>
@@ -3604,27 +4564,41 @@
           <t>러그 3 · 표시 바퀴 4 + 여분</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>지름 6 두께 3, 옵션 "40개입"</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7119515778</t>
         </is>
@@ -3652,27 +4626,41 @@
           <t>클러치·브레이크 페달 2 · 핸들 1 + 여분 2</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>D(반달)축 국내품이 없어 톱니 축 → 페달 팔(80)·핸들 캠(93)의 축 구멍을 압입 구멍(POT_HOLE)으로 바꿈. B(직선형)·가운데 딸깍은 화면 미표기 → 받으면 확인</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>10K, 16mm, 축 15mm, 부싱 M7. 옵션 "가변저항 10K"</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/8718871111</t>
         </is>
@@ -3700,23 +4688,41 @@
           <t>덮개 열림 감지 1 + 여분 1</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>레버형, 3핀 (C–NO 사용)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9167678186</t>
         </is>
@@ -3746,25 +4752,41 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
+          <t>1개면 됨</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
           <t>동신전자로 묶음 (5,300 → 1,300)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>옵션 "(PP-A848) 점퍼케이블 40핀 40cm 암/수"</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9183828363</t>
         </is>
@@ -3792,27 +4814,41 @@
           <t>센서 배선 기판</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>20장 묶음이 16,900 으로 올라 필요한 장수만</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>옵션 "(PP-D021) 에폭시 양면기판 28x43"</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9181560693</t>
         </is>
@@ -3840,27 +4876,41 @@
           <t>모터 주 스위치</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>값 낮춤: 여분 뺌</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>코일 12V, 접점 30A 이상</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/6667848502</t>
         </is>
@@ -3888,27 +4938,41 @@
           <t>배터리 + 단자 바로 옆</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>그대로 (여분 퓨즈 포함)</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>15A 퓨즈 포함</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9663070188</t>
         </is>
@@ -3936,27 +5000,41 @@
           <t>운영자 비상 차단 (릴레이 코일 회로, b접점)</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>G마켓 스위치 + 11번가 박스 대신 한 세트 (동신전자)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>b접점 있음 (1·2번 NC), 장착 Ø22.5, 박스 BXA-22/1/Y 포함. KC 미인증 표기</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9169916764</t>
         </is>
@@ -3984,27 +5062,41 @@
           <t>아두이노 감시 → 주 릴레이 코일 차단</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>동신전자로 묶음</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>5V, 1채널 (트리거 방식은 펌웨어로 맞춤)</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9162331915</t>
         </is>
@@ -4032,27 +5124,41 @@
           <t>주 릴레이 코일 역기전력 흡수 + 여분</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>하진전자로 묶음</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>1N4007</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9705767581</t>
         </is>
@@ -4080,27 +5186,41 @@
           <t>안전 회로 감지 분압 (12V → 아두이노 A4)</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>30종 세트 대신 필요한 값만</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>옵션 "10K"</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
@@ -4128,27 +5248,41 @@
           <t>안전 회로 감지 분압</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>같은 상품의 다른 옵션</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>옵션 "4.7K"</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9701925630</t>
         </is>
@@ -4176,27 +5310,41 @@
           <t>배터리-퓨즈-릴레이-모터 드라이버 (2m 필요 + 여분 1m)</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>16AWG 이상</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/7225302003</t>
         </is>
@@ -4224,27 +5372,41 @@
           <t>퓨즈 홀더·릴레이 소켓 연결 + 여분 (압착 실수)</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F79" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>동신전자로 묶음 (전과 같은 10개)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>6.3mm 암, 절연형 (전선 굵기 범위 화면 미표기)</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>https://www.coupang.com/vp/products/9181548711</t>
         </is>
@@ -4272,25 +5434,61 @@
           <t>판매처 17곳: 3,000 × 10 · 3,500 × 2 · 4,000 · 2,800 × 2 · 2,700 · 2,500 (2026-10-23 화면). 로켓배송 12개와 무료배송 9곳은 0. 제주·도서산간 추가 제외</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>쿠팡 화면 2026-10-23</t>
-        </is>
-      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>판매자를 줄이고 로켓배송(19,800 이상 무료)으로 묶음</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>쿠팡 화면 2026-10-23</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>판매처별 배송비 (링크 없음)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>예상단가: 쿠팡·11번가 화면 2026-10-23 (다른 세션에서 확인). 모두 국내배송. 공구 중 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더(4인치 가정)는 보유. 캘리퍼스는 사지 않음 (사용자 결정 2026-10-23). 레일 칼라는 국내배송 상품이 없어 출력 (50c).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>부족 검산: 79줄 중 부족 0줄. 여분 없는 줄(아크릴·레오나르도·릴레이·비상정지 등)은 값을 줄이며 여분을 뺀 것. 구매 목록 밖 준비물: 캘리퍼스 (D컷·쿠폰·스프링 k·가변저항 축·봉 지름, 빌림), 톱 (MDF 1200 → 750 + 450), 커터칼 (덮개 바닥 막·코르크), 사포 (75 보스 등 다듬기), 네임펜 (D컷 표시), 실납 (납땜), 펜치 (압착 단자: 압착 공구가 없으면 펜치로 누른 뒤 납땜), 드라이버, 딱풀 (출력 바닥), 계량컵·생수병 (물 무게 시험). 육각 렌치·전동 드릴·납땜 인두·멀티미터·앵글 그라인더는 보유.</t>
         </is>
       </c>
     </row>
